--- a/data/Outdoor plants.xlsx
+++ b/data/Outdoor plants.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B669DAD4-E91F-49F5-A303-CB4B55738398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD10AC1-FF5C-4760-ABD8-2D6A1FB99AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B519764-563C-4CD5-B8E9-9B8B0702B21B}"/>
   </bookViews>
@@ -1411,9 +1411,6 @@
     <t>طاووس الجنة</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/KzM2QdvT/Caesalpinia-pulcherrima.jpg</t>
-  </si>
-  <si>
     <t>Location type</t>
   </si>
   <si>
@@ -1553,13 +1550,16 @@
   </si>
   <si>
     <t>Gate 3-S55</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/fWm1rQJy/Caesalpinia-pulcherrima.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2058,32 +2058,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43C3B61-471E-4868-9D01-BC7FF88A37C8}">
   <dimension ref="A1:U186"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4"/>
-    <col min="2" max="2" width="32.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="47.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="4" customWidth="1"/>
-    <col min="12" max="13" width="9.140625" style="4"/>
-    <col min="14" max="14" width="14.140625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="4" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.140625" style="4" customWidth="1"/>
-    <col min="20" max="20" width="27.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="33.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="9.1796875" style="4"/>
+    <col min="2" max="2" width="32.453125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="47.81640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1796875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" style="4" customWidth="1"/>
+    <col min="12" max="13" width="9.1796875" style="4"/>
+    <col min="14" max="14" width="14.1796875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="16.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.1796875" style="4" customWidth="1"/>
+    <col min="20" max="20" width="27.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.45">
+    <row r="1" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.45">
+    <row r="2" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14.45">
+    <row r="3" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="14.45">
+    <row r="4" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>49</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14.45">
+    <row r="5" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="14.45">
+    <row r="6" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>66</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14.45">
+    <row r="7" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>75</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="14.45">
+    <row r="8" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>82</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.45">
+    <row r="9" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>92</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14.45">
+    <row r="10" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>97</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="14.45">
+    <row r="11" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>104</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="14.45">
+    <row r="12" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>111</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14.45">
+    <row r="13" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>115</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="14.45">
+    <row r="14" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>122</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="14.45">
+    <row r="15" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>129</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15.75">
+    <row r="16" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>136</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="14.45">
+    <row r="17" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>143</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="14.45">
+    <row r="18" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>150</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="14.45">
+    <row r="19" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>159</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="14.45">
+    <row r="20" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>167</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="14.45">
+    <row r="21" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>175</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="14.45">
+    <row r="22" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>183</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="14.45">
+    <row r="23" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>192</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="14.45">
+    <row r="24" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>198</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="14.45">
+    <row r="25" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>206</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="14.45">
+    <row r="26" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>214</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="14.45">
+    <row r="27" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>221</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="14.45">
+    <row r="28" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>228</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="14.45">
+    <row r="29" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>236</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="14.45">
+    <row r="30" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>242</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="14.45">
+    <row r="31" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>250</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1">
+    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>257</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="14.45">
+    <row r="33" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>265</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="14.45">
+    <row r="34" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>271</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="14.45">
+    <row r="35" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>277</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="14.45">
+    <row r="36" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>283</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="14.45">
+    <row r="37" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>290</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="14.45">
+    <row r="38" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>295</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="14.45">
+    <row r="39" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>301</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="14.45">
+    <row r="40" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>306</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="14.45">
+    <row r="41" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>313</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="14.45">
+    <row r="42" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>321</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="14.45">
+    <row r="43" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>327</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="14.45">
+    <row r="44" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>333</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="14.45">
+    <row r="45" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>338</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="14.45">
+    <row r="46" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>342</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="14.45">
+    <row r="47" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>349</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="14.45">
+    <row r="48" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>356</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="14.45">
+    <row r="49" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>364</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="14.45">
+    <row r="50" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>371</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="14.45">
+    <row r="51" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>377</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="14.45">
+    <row r="52" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>384</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="14.45">
+    <row r="53" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>390</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="14.45">
+    <row r="54" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>398</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="14.45">
+    <row r="55" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>405</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="14.45">
+    <row r="56" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>410</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="14.45">
+    <row r="57" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>418</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="14.45">
+    <row r="58" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="25" t="s">
         <v>425</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="14.45">
+    <row r="59" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="25" t="s">
         <v>432</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="14.45">
+    <row r="60" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="25" t="s">
         <v>439</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="14.45" customHeight="1">
+    <row r="61" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="24" t="s">
         <v>446</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="14.45" customHeight="1">
+    <row r="62" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="25" t="s">
         <v>453</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>24</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
       <c r="F62" s="25" t="s">
         <v>70</v>
@@ -6113,130 +6113,130 @@
         <v>452</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="14.45"/>
-    <row r="64" spans="1:21" ht="14.45"/>
-    <row r="65" ht="14.45"/>
-    <row r="66" ht="14.45"/>
-    <row r="67" ht="14.45"/>
-    <row r="68" ht="14.45"/>
-    <row r="69" ht="14.45"/>
-    <row r="70" ht="14.45"/>
-    <row r="71" ht="14.45"/>
-    <row r="72" ht="14.45"/>
-    <row r="73" ht="14.45"/>
-    <row r="74" ht="14.45"/>
-    <row r="75" ht="14.45"/>
-    <row r="76" ht="14.45"/>
-    <row r="77" ht="14.45"/>
-    <row r="78" ht="14.45"/>
-    <row r="79" ht="14.45"/>
-    <row r="80" ht="14.45"/>
-    <row r="81" ht="14.45"/>
-    <row r="82" ht="14.45"/>
-    <row r="83" ht="14.45"/>
-    <row r="84" ht="14.45"/>
-    <row r="85" ht="14.45"/>
-    <row r="86" ht="14.45"/>
-    <row r="87" ht="14.45"/>
-    <row r="88" ht="14.45"/>
-    <row r="89" ht="14.45"/>
-    <row r="90" ht="14.45"/>
-    <row r="91" ht="14.45"/>
-    <row r="92" ht="14.45"/>
-    <row r="93" ht="14.45"/>
-    <row r="94" ht="14.45"/>
-    <row r="95" ht="14.45"/>
-    <row r="96" ht="14.45"/>
-    <row r="97" ht="14.45"/>
-    <row r="98" ht="14.45"/>
-    <row r="99" ht="14.45"/>
-    <row r="100" ht="14.45"/>
-    <row r="101" ht="14.45"/>
-    <row r="102" ht="14.45"/>
-    <row r="103" ht="14.45"/>
-    <row r="104" ht="14.45"/>
-    <row r="105" ht="14.45"/>
-    <row r="106" ht="14.45"/>
-    <row r="107" ht="14.45"/>
-    <row r="108" ht="14.45"/>
-    <row r="109" ht="14.45"/>
-    <row r="110" ht="14.45"/>
-    <row r="111" ht="14.45"/>
-    <row r="112" ht="14.45"/>
-    <row r="113" ht="14.45"/>
-    <row r="114" ht="14.45"/>
-    <row r="115" ht="14.45"/>
-    <row r="116" ht="14.45"/>
-    <row r="117" ht="14.45"/>
-    <row r="118" ht="14.45"/>
-    <row r="119" ht="14.45"/>
-    <row r="120" ht="14.45"/>
-    <row r="121" ht="14.45"/>
-    <row r="122" ht="14.45"/>
-    <row r="123" ht="14.45"/>
-    <row r="124" ht="14.45"/>
-    <row r="125" ht="14.45"/>
-    <row r="126" ht="14.45"/>
-    <row r="127" ht="14.45"/>
-    <row r="128" ht="14.45"/>
-    <row r="129" ht="14.45"/>
-    <row r="130" ht="14.45"/>
-    <row r="131" ht="14.45"/>
-    <row r="132" ht="14.45"/>
-    <row r="133" ht="14.45"/>
-    <row r="134" ht="14.45"/>
-    <row r="135" ht="14.45"/>
-    <row r="136" ht="14.45"/>
-    <row r="137" ht="14.45"/>
-    <row r="138" ht="14.45"/>
-    <row r="139" ht="14.45"/>
-    <row r="140" ht="14.45"/>
-    <row r="141" ht="14.45"/>
-    <row r="142" ht="14.45"/>
-    <row r="143" ht="14.45"/>
-    <row r="144" ht="14.45"/>
-    <row r="145" ht="14.45"/>
-    <row r="146" ht="14.45"/>
-    <row r="147" ht="14.45"/>
-    <row r="148" ht="14.45"/>
-    <row r="149" ht="14.45"/>
-    <row r="150" ht="14.45"/>
-    <row r="151" ht="14.45"/>
-    <row r="152" ht="14.45"/>
-    <row r="153" ht="14.45"/>
-    <row r="154" ht="14.45"/>
-    <row r="155" ht="14.45"/>
-    <row r="156" ht="14.45"/>
-    <row r="157" ht="14.45"/>
-    <row r="158" ht="14.45"/>
-    <row r="159" ht="14.45"/>
-    <row r="160" ht="14.45"/>
-    <row r="161" ht="14.45"/>
-    <row r="162" ht="14.45"/>
-    <row r="163" ht="14.45"/>
-    <row r="164" ht="14.45"/>
-    <row r="165" ht="14.45"/>
-    <row r="166" ht="14.45"/>
-    <row r="167" ht="14.45"/>
-    <row r="168" ht="14.45"/>
-    <row r="169" ht="14.45"/>
-    <row r="170" ht="14.45"/>
-    <row r="171" ht="14.45"/>
-    <row r="172" ht="14.45"/>
-    <row r="173" ht="14.45"/>
-    <row r="174" ht="14.45"/>
-    <row r="175" ht="14.45"/>
-    <row r="176" ht="14.45"/>
-    <row r="177" ht="14.45"/>
-    <row r="178" ht="14.45"/>
-    <row r="179" ht="14.45"/>
-    <row r="180" ht="14.45"/>
-    <row r="181" ht="14.45"/>
-    <row r="182" ht="14.45"/>
-    <row r="183" ht="14.45"/>
-    <row r="184" ht="14.45"/>
-    <row r="185" ht="14.45"/>
-    <row r="186" ht="14.45"/>
+    <row r="63" spans="1:21" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:21" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="115" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="116" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="117" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="118" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="120" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="121" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="122" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="123" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="124" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="125" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="126" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="127" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="128" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="130" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="131" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="132" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="133" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="134" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="135" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="136" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="137" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="138" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="139" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="140" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="141" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="142" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="143" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="144" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U45">
     <sortCondition ref="A2:A45"/>
@@ -6408,897 +6408,897 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G163"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="50.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="34.28515625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="50.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="6" max="6" width="34.26953125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="26.25" customHeight="1">
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C1" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="D1" s="20" t="s">
+    </row>
+    <row r="2" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="B2" s="20" t="s">
         <v>461</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>462</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
     </row>
-    <row r="3" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="3" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21"/>
     </row>
-    <row r="4" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="4" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="21"/>
     </row>
-    <row r="5" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="5" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="6" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
     </row>
-    <row r="7" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="7" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="8" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="9" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C10" s="21"/>
       <c r="E10" s="21"/>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C12" s="23"/>
       <c r="E12" s="22"/>
       <c r="F12" s="21"/>
     </row>
-    <row r="13" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
     </row>
-    <row r="17" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C17" s="21"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
     </row>
-    <row r="20" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
     </row>
-    <row r="21" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
     </row>
-    <row r="22" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
     </row>
-    <row r="23" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
     </row>
-    <row r="30" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
     </row>
-    <row r="31" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
     </row>
-    <row r="35" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
     </row>
-    <row r="36" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
     </row>
-    <row r="38" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
     </row>
-    <row r="39" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
     </row>
-    <row r="42" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
     </row>
-    <row r="43" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
     </row>
-    <row r="44" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="44" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
     </row>
-    <row r="45" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
     </row>
-    <row r="46" spans="1:7" ht="14.45">
+    <row r="46" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="20"/>
       <c r="E46" s="16"/>
       <c r="F46" s="17"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:7" ht="14.45">
+    <row r="47" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="E47" s="16"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" ht="14.45">
+    <row r="48" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F48" s="18"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="6:7" ht="14.45">
+    <row r="49" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F49" s="18"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="6:7" ht="14.45">
+    <row r="50" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F50" s="18"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="6:7" ht="14.45">
+    <row r="51" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F51" s="18"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="6:7" ht="14.45">
+    <row r="52" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F52" s="18"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="6:7" ht="14.45">
+    <row r="53" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F53" s="18"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="6:7" ht="14.45">
+    <row r="54" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F54" s="18"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="6:7" ht="14.45">
+    <row r="55" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F55" s="18"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="6:7" ht="14.45">
+    <row r="56" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F56" s="18"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="6:7" ht="14.45">
+    <row r="57" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F57" s="18"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="6:7" ht="14.45">
+    <row r="58" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F58" s="18"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="6:7" ht="14.45">
+    <row r="59" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F59" s="18"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="6:7" ht="14.45">
+    <row r="60" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F60" s="18"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="6:7" ht="14.45">
+    <row r="61" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F61" s="18"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="6:7" ht="14.45">
+    <row r="62" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F62" s="18"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="6:7" ht="14.45">
+    <row r="63" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F63" s="18"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="6:7" ht="14.45">
+    <row r="64" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F64" s="18"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="6:7" ht="14.45">
+    <row r="65" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F65" s="18"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="6:7" ht="14.45">
+    <row r="66" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F66" s="18"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="6:7" ht="14.45">
+    <row r="67" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F67" s="18"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="6:7" ht="14.45">
+    <row r="68" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F68" s="18"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="6:7" ht="14.45">
+    <row r="69" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F69" s="18"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="6:7" ht="14.45">
+    <row r="70" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F70" s="18"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="6:7" ht="14.45">
+    <row r="71" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F71" s="18"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="6:7" ht="14.45">
+    <row r="72" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F72" s="18"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="6:7" ht="14.45">
+    <row r="73" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F73" s="18"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="6:7" ht="14.45">
+    <row r="74" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="6:7" ht="14.45">
+    <row r="75" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="6:7" ht="14.45">
+    <row r="76" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="6:7" ht="14.45">
+    <row r="77" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="6:7" ht="14.45">
+    <row r="78" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="6:7" ht="14.45">
+    <row r="79" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="6:7" ht="14.45">
+    <row r="80" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="6:7" ht="14.45">
+    <row r="81" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="6:7" ht="14.45">
+    <row r="82" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="6:7" ht="14.45">
+    <row r="83" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="6:7" ht="14.45">
+    <row r="84" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="6:7" ht="14.45">
+    <row r="85" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="6:7" ht="14.45">
+    <row r="86" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="6:7" ht="14.45">
+    <row r="87" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="6:7" ht="14.45">
+    <row r="88" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="6:7" ht="14.45">
+    <row r="89" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="6:7" ht="14.45">
+    <row r="90" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="6:7" ht="14.45">
+    <row r="91" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="6:7" ht="14.45">
+    <row r="92" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="6:7" ht="14.45">
+    <row r="93" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="6:7" ht="15.6">
+    <row r="94" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F94" s="19"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="6:7" ht="15.6">
+    <row r="95" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F95" s="19"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="6:7" ht="15.6">
+    <row r="96" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F96" s="19"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="6:7" ht="15.6">
+    <row r="97" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F97" s="19"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="6:7" ht="15.6">
+    <row r="98" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F98" s="19"/>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="6:7" ht="15.6">
+    <row r="99" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F99" s="19"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="6:7" ht="15.6">
+    <row r="100" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F100" s="19"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="6:7" ht="15.6">
+    <row r="101" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F101" s="19"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="6:7" ht="15.6">
+    <row r="102" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F102" s="19"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="6:7" ht="15.6">
+    <row r="103" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F103" s="19"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="6:7" ht="15.6">
+    <row r="104" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F104" s="19"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="6:7" ht="15.6">
+    <row r="105" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F105" s="19"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="6:7" ht="15.6">
+    <row r="106" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F106" s="19"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="6:7" ht="15.6">
+    <row r="107" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F107" s="19"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="6:7" ht="15.6">
+    <row r="108" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F108" s="19"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="6:7" ht="15.6">
+    <row r="109" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F109" s="19"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="6:7" ht="15.6">
+    <row r="110" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F110" s="19"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="6:7" ht="15.6">
+    <row r="111" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F111" s="19"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="6:7" ht="15.6">
+    <row r="112" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F112" s="19"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="6:7" ht="15.6">
+    <row r="113" spans="6:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F113" s="19"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="6:7" ht="14.45">
+    <row r="114" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F114" s="18"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="6:7" ht="14.45">
+    <row r="115" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F115" s="18"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="6:7" ht="14.45">
+    <row r="116" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F116" s="18"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="6:7" ht="14.45">
+    <row r="117" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F117" s="18"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="6:7" ht="14.45">
+    <row r="118" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F118" s="18"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="6:7" ht="14.45">
+    <row r="119" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F119" s="18"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="6:7" ht="14.45">
+    <row r="120" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F120" s="18"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="6:7" ht="14.45">
+    <row r="121" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F121" s="18"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="6:7" ht="14.45">
+    <row r="122" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F122" s="18"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="6:7" ht="14.45">
+    <row r="123" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F123" s="18"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="6:7" ht="14.45">
+    <row r="124" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F124" s="18"/>
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="6:7" ht="14.45">
+    <row r="125" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F125" s="18"/>
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="6:7" ht="14.45">
+    <row r="126" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F126" s="18"/>
       <c r="G126" s="1"/>
     </row>
-    <row r="127" spans="6:7" ht="14.45">
+    <row r="127" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F127" s="18"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="6:7" ht="14.45">
+    <row r="128" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F128" s="18"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="6:7" ht="14.45">
+    <row r="129" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F129" s="18"/>
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="6:7" ht="14.45">
+    <row r="130" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F130" s="18"/>
       <c r="G130" s="1"/>
     </row>
-    <row r="131" spans="6:7" ht="14.45">
+    <row r="131" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F131" s="18"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" spans="6:7" ht="14.45">
+    <row r="132" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="F132" s="18"/>
       <c r="G132" s="1"/>
     </row>
-    <row r="133" spans="6:7" ht="14.45">
+    <row r="133" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G133" s="1"/>
     </row>
-    <row r="134" spans="6:7" ht="14.45">
+    <row r="134" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G134" s="1"/>
     </row>
-    <row r="135" spans="6:7" ht="14.45">
+    <row r="135" spans="6:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G135" s="1"/>
     </row>
-    <row r="136" spans="6:7" ht="15" customHeight="1">
+    <row r="136" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G136" s="1"/>
     </row>
-    <row r="137" spans="6:7" ht="15" customHeight="1">
+    <row r="137" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="6:7" ht="15" customHeight="1">
+    <row r="138" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G138" s="1"/>
     </row>
-    <row r="139" spans="6:7" ht="15" customHeight="1">
+    <row r="139" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G139" s="1"/>
     </row>
-    <row r="140" spans="6:7" ht="15" customHeight="1">
+    <row r="140" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G140" s="1"/>
     </row>
-    <row r="141" spans="6:7" ht="15" customHeight="1">
+    <row r="141" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G141" s="1"/>
     </row>
-    <row r="142" spans="6:7" ht="15" customHeight="1">
+    <row r="142" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G142" s="1"/>
     </row>
-    <row r="143" spans="6:7" ht="15" customHeight="1">
+    <row r="143" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G143" s="1"/>
     </row>
-    <row r="144" spans="6:7" ht="15" customHeight="1">
+    <row r="144" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G144" s="1"/>
     </row>
-    <row r="145" spans="7:7" ht="15" customHeight="1">
+    <row r="145" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G145" s="1"/>
     </row>
-    <row r="146" spans="7:7" ht="15" customHeight="1">
+    <row r="146" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G146" s="1"/>
     </row>
-    <row r="147" spans="7:7" ht="15" customHeight="1">
+    <row r="147" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G147" s="1"/>
     </row>
-    <row r="148" spans="7:7" ht="15" customHeight="1">
+    <row r="148" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G148" s="1"/>
     </row>
-    <row r="149" spans="7:7" ht="15" customHeight="1">
+    <row r="149" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G149" s="1"/>
     </row>
-    <row r="150" spans="7:7" ht="15" customHeight="1">
+    <row r="150" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G150" s="1"/>
     </row>
-    <row r="151" spans="7:7" ht="15" customHeight="1">
+    <row r="151" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G151" s="1"/>
     </row>
-    <row r="152" spans="7:7" ht="15" customHeight="1">
+    <row r="152" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G152" s="1"/>
     </row>
-    <row r="153" spans="7:7" ht="15" customHeight="1">
+    <row r="153" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G153" s="1"/>
     </row>
-    <row r="154" spans="7:7" ht="15" customHeight="1">
+    <row r="154" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G154" s="1"/>
     </row>
-    <row r="155" spans="7:7" ht="15" customHeight="1">
+    <row r="155" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G155" s="1"/>
     </row>
-    <row r="156" spans="7:7" ht="15" customHeight="1">
+    <row r="156" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G156" s="1"/>
     </row>
-    <row r="157" spans="7:7" ht="15" customHeight="1">
+    <row r="157" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G157" s="1"/>
     </row>
-    <row r="158" spans="7:7" ht="15" customHeight="1">
+    <row r="158" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G158" s="1"/>
     </row>
-    <row r="159" spans="7:7" ht="15" customHeight="1">
+    <row r="159" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G159" s="1"/>
     </row>
-    <row r="160" spans="7:7" ht="15" customHeight="1">
+    <row r="160" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G160" s="1"/>
     </row>
-    <row r="161" spans="7:7" ht="15" customHeight="1">
+    <row r="161" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G161" s="1"/>
     </row>
-    <row r="162" spans="7:7" ht="15" customHeight="1">
+    <row r="162" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G162" s="1"/>
     </row>
-    <row r="163" spans="7:7" ht="15" customHeight="1">
+    <row r="163" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G163" s="1"/>
     </row>
   </sheetData>
@@ -7330,14 +7330,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D89A625C5B6364BB7302BED22ED65DA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="05bac8ad6e033965382d52c38353e541">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7855343b-5261-4afc-a17c-d4c130fbaa85" xmlns:ns4="72f917e0-5d36-43ac-975d-26afa4cf7fc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="452e5605b09f318b6d66379e79837bd5" ns3:_="" ns4:_="">
     <xsd:import namespace="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
@@ -7584,14 +7576,47 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56978299-3DC6-451D-A1E5-57FB07C431CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
+    <ds:schemaRef ds:uri="72f917e0-5d36-43ac-975d-26afa4cf7fc0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56978299-3DC6-451D-A1E5-57FB07C431CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Outdoor plants.xlsx
+++ b/data/Outdoor plants.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD10AC1-FF5C-4760-ABD8-2D6A1FB99AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A26559-EA27-44D2-B816-AA963C6989A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B519764-563C-4CD5-B8E9-9B8B0702B21B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="505">
   <si>
     <t>Plant ID</t>
   </si>
@@ -1553,6 +1553,9 @@
   </si>
   <si>
     <t>https://i.postimg.cc/fWm1rQJy/Caesalpinia-pulcherrima.jpg</t>
+  </si>
+  <si>
+    <t>Portable</t>
   </si>
 </sst>
 </file>
@@ -2057,7 +2060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43C3B61-471E-4868-9D01-BC7FF88A37C8}">
-  <dimension ref="A1:U186"/>
+  <dimension ref="A1:V186"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="4"/>
@@ -2083,7 +2086,7 @@
     <col min="22" max="16384" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2147,8 +2150,11 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V1" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
@@ -2212,8 +2218,11 @@
       <c r="U2" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
@@ -2277,8 +2286,11 @@
       <c r="U3" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>49</v>
       </c>
@@ -2342,8 +2354,11 @@
       <c r="U4" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V4" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
@@ -2407,8 +2422,11 @@
       <c r="U5" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V5" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>66</v>
       </c>
@@ -2472,8 +2490,11 @@
       <c r="U6" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>75</v>
       </c>
@@ -2537,8 +2558,11 @@
       <c r="U7" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>82</v>
       </c>
@@ -2602,8 +2626,11 @@
       <c r="U8" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V8" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>92</v>
       </c>
@@ -2667,8 +2694,11 @@
       <c r="U9" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V9" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>97</v>
       </c>
@@ -2732,8 +2762,11 @@
       <c r="U10" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V10" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>104</v>
       </c>
@@ -2797,8 +2830,11 @@
       <c r="U11" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>111</v>
       </c>
@@ -2862,8 +2898,11 @@
       <c r="U12" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V12" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>115</v>
       </c>
@@ -2927,8 +2966,11 @@
       <c r="U13" s="8" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V13" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>122</v>
       </c>
@@ -2992,8 +3034,11 @@
       <c r="U14" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V14" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>129</v>
       </c>
@@ -3057,8 +3102,11 @@
       <c r="U15" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V15" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>136</v>
       </c>
@@ -3122,8 +3170,11 @@
       <c r="U16" s="4" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V16" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>143</v>
       </c>
@@ -3187,8 +3238,11 @@
       <c r="U17" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V17" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>150</v>
       </c>
@@ -3252,8 +3306,11 @@
       <c r="U18" s="8" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V18" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>159</v>
       </c>
@@ -3317,8 +3374,11 @@
       <c r="U19" s="8" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V19" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>167</v>
       </c>
@@ -3382,8 +3442,11 @@
       <c r="U20" s="8" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V20" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>175</v>
       </c>
@@ -3447,8 +3510,11 @@
       <c r="U21" s="8" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V21" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>183</v>
       </c>
@@ -3512,8 +3578,11 @@
       <c r="U22" s="8" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V22" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>192</v>
       </c>
@@ -3577,8 +3646,11 @@
       <c r="U23" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V23" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>198</v>
       </c>
@@ -3642,8 +3714,11 @@
       <c r="U24" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V24" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>206</v>
       </c>
@@ -3707,8 +3782,11 @@
       <c r="U25" s="4" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V25" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>214</v>
       </c>
@@ -3772,8 +3850,11 @@
       <c r="U26" s="4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V26" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>221</v>
       </c>
@@ -3837,8 +3918,11 @@
       <c r="U27" s="4" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V27" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>228</v>
       </c>
@@ -3902,8 +3986,11 @@
       <c r="U28" s="4" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V28" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>236</v>
       </c>
@@ -3967,8 +4054,11 @@
       <c r="U29" s="4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V29" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>242</v>
       </c>
@@ -4032,8 +4122,11 @@
       <c r="U30" s="4" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V30" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>250</v>
       </c>
@@ -4097,8 +4190,11 @@
       <c r="U31" s="4" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V31" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>257</v>
       </c>
@@ -4162,8 +4258,11 @@
       <c r="U32" s="4" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V32" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>265</v>
       </c>
@@ -4227,8 +4326,11 @@
       <c r="U33" s="4" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>271</v>
       </c>
@@ -4292,8 +4394,11 @@
       <c r="U34" s="4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V34" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>277</v>
       </c>
@@ -4357,8 +4462,11 @@
       <c r="U35" s="4" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V35" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>283</v>
       </c>
@@ -4422,8 +4530,11 @@
       <c r="U36" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V36" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>290</v>
       </c>
@@ -4487,8 +4598,11 @@
       <c r="U37" s="4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V37" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>295</v>
       </c>
@@ -4552,8 +4666,11 @@
       <c r="U38" s="4" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V38" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>301</v>
       </c>
@@ -4617,8 +4734,11 @@
       <c r="U39" s="4" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V39" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>306</v>
       </c>
@@ -4682,8 +4802,11 @@
       <c r="U40" s="4" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V40" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>313</v>
       </c>
@@ -4747,8 +4870,11 @@
       <c r="U41" s="4" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V41" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>321</v>
       </c>
@@ -4812,8 +4938,11 @@
       <c r="U42" s="4" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V42" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>327</v>
       </c>
@@ -4877,8 +5006,11 @@
       <c r="U43" s="4" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V43" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>333</v>
       </c>
@@ -4942,8 +5074,11 @@
       <c r="U44" s="4" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V44" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>338</v>
       </c>
@@ -5007,8 +5142,11 @@
       <c r="U45" s="4" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V45" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>342</v>
       </c>
@@ -5072,8 +5210,11 @@
       <c r="U46" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V46" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>349</v>
       </c>
@@ -5137,8 +5278,11 @@
       <c r="U47" s="4" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V47" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>356</v>
       </c>
@@ -5202,8 +5346,11 @@
       <c r="U48" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V48" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>364</v>
       </c>
@@ -5267,8 +5414,11 @@
       <c r="U49" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V49" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>371</v>
       </c>
@@ -5332,8 +5482,11 @@
       <c r="U50" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V50" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>377</v>
       </c>
@@ -5397,8 +5550,11 @@
       <c r="U51" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V51" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>384</v>
       </c>
@@ -5462,8 +5618,11 @@
       <c r="U52" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V52" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>390</v>
       </c>
@@ -5527,8 +5686,11 @@
       <c r="U53" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V53" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>398</v>
       </c>
@@ -5592,8 +5754,11 @@
       <c r="U54" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V54" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>405</v>
       </c>
@@ -5657,8 +5822,11 @@
       <c r="U55" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V55" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>410</v>
       </c>
@@ -5722,8 +5890,11 @@
       <c r="U56" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V56" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>418</v>
       </c>
@@ -5787,8 +5958,11 @@
       <c r="U57" s="4" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V57" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="25" t="s">
         <v>425</v>
       </c>
@@ -5852,8 +6026,11 @@
       <c r="U58" s="25" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V58" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="25" t="s">
         <v>432</v>
       </c>
@@ -5917,8 +6094,11 @@
       <c r="U59" s="25" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="V59" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="25" t="s">
         <v>439</v>
       </c>
@@ -5982,8 +6162,11 @@
       <c r="U60" s="25" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V60" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="24" t="s">
         <v>446</v>
       </c>
@@ -6047,8 +6230,11 @@
       <c r="U61" s="24" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V61" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="25" t="s">
         <v>453</v>
       </c>
@@ -6112,9 +6298,12 @@
       <c r="U62" s="25" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:21" ht="14.5" x14ac:dyDescent="0.35"/>
+      <c r="V62" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="65" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="66" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="67" ht="14.5" x14ac:dyDescent="0.35"/>
@@ -6253,7 +6442,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M18 S2:S1048576 P2:Q1048576 H2:H1048576 M26:M1048576" xr:uid="{26BEA281-5615-4C1E-80B9-785C1C126E1E}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L18 N2:N1048576 L26:L1048576" xr:uid="{BADEB7D1-F197-43A2-9AAB-F8E1A586A330}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L18 N2:N1048576 L26:L1048576 V2:V1048576" xr:uid="{BADEB7D1-F197-43A2-9AAB-F8E1A586A330}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{9B94FA55-E999-447C-AE3A-D83167D0511E}">
@@ -7330,6 +7519,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D89A625C5B6364BB7302BED22ED65DA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="05bac8ad6e033965382d52c38353e541">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7855343b-5261-4afc-a17c-d4c130fbaa85" xmlns:ns4="72f917e0-5d36-43ac-975d-26afa4cf7fc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="452e5605b09f318b6d66379e79837bd5" ns3:_="" ns4:_="">
     <xsd:import namespace="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
@@ -7576,14 +7773,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
   <ds:schemaRefs>
@@ -7593,6 +7782,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56978299-3DC6-451D-A1E5-57FB07C431CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7609,14 +7808,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/Outdoor plants.xlsx
+++ b/data/Outdoor plants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A26559-EA27-44D2-B816-AA963C6989A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BE3DB1-27BA-4371-BA64-E2E38D7641AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B519764-563C-4CD5-B8E9-9B8B0702B21B}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$57</definedName>
-    <definedName name="PlantList">Sheet1!$B$2:$B$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$48</definedName>
+    <definedName name="PlantList">Sheet1!$B$2:$B$280</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="448">
   <si>
     <t>Plant ID</t>
   </si>
@@ -271,24 +271,6 @@
     <t>OP-006</t>
   </si>
   <si>
-    <t>Dianthus spp.</t>
-  </si>
-  <si>
-    <t>القرنفل</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/tJtggjJn/Dianthus-spp.jpg</t>
-  </si>
-  <si>
-    <t>0.15 - 0.9 m</t>
-  </si>
-  <si>
-    <t>237g/year</t>
-  </si>
-  <si>
-    <t>44g/year</t>
-  </si>
-  <si>
     <t>OP-007</t>
   </si>
   <si>
@@ -379,15 +361,6 @@
     <t>OP-011</t>
   </si>
   <si>
-    <t>Euphorbia</t>
-  </si>
-  <si>
-    <t>الفربيون</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/dtYkcW3T/Euphorbia.jpg</t>
-  </si>
-  <si>
     <t>OP-013</t>
   </si>
   <si>
@@ -433,45 +406,9 @@
     <t>OP-015</t>
   </si>
   <si>
-    <t>Dracaena angolensis</t>
-  </si>
-  <si>
-    <t>نبات الثعبان الأسطواني</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/VN60Hd6G/Dracaena-angolensis.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1.5 m </t>
-  </si>
-  <si>
-    <t>500-1,250 g/year</t>
-  </si>
-  <si>
-    <t>690-1,720 g/year</t>
-  </si>
-  <si>
     <t>OP-016</t>
   </si>
   <si>
-    <t>Cyperus aternifolius</t>
-  </si>
-  <si>
-    <t>نبات المظلة</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/mrtvb3SH/cyperus-alternifolius.jpg</t>
-  </si>
-  <si>
-    <t>1 - 1.2 m</t>
-  </si>
-  <si>
-    <t>500-2,500 g/year</t>
-  </si>
-  <si>
-    <t>2,060 g/year</t>
-  </si>
-  <si>
     <t>OP-017</t>
   </si>
   <si>
@@ -595,30 +532,9 @@
     <t>OP-023</t>
   </si>
   <si>
-    <t>Ficus spp</t>
-  </si>
-  <si>
-    <t>الفيكس</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/Qdqcy2qt/Ficus-spp-1.jpg</t>
-  </si>
-  <si>
-    <t>10 - 30 m</t>
-  </si>
-  <si>
-    <t>10 - 20 m</t>
-  </si>
-  <si>
     <t>Adventitious</t>
   </si>
   <si>
-    <t>12,000-18,000g/year</t>
-  </si>
-  <si>
-    <t>40,000-100,000g/year</t>
-  </si>
-  <si>
     <t>OP-024</t>
   </si>
   <si>
@@ -640,27 +556,9 @@
     <t>OP-025</t>
   </si>
   <si>
-    <t>Ligustrum spp</t>
-  </si>
-  <si>
-    <t>تمرحنا</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/509hdWv2/Ligustrum-spp.jpg</t>
-  </si>
-  <si>
-    <t>4 - 5 m</t>
-  </si>
-  <si>
-    <t>2 - 3 m</t>
-  </si>
-  <si>
     <t>4,000-6,000g/year</t>
   </si>
   <si>
-    <t>12,000-35,000g/year</t>
-  </si>
-  <si>
     <t>OP-026</t>
   </si>
   <si>
@@ -709,24 +607,6 @@
     <t>OP-028</t>
   </si>
   <si>
-    <t>Tabebuia spp</t>
-  </si>
-  <si>
-    <t>شجرة التابوبيا</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/zBd9q2SS/Tabebuia-spp.jpg</t>
-  </si>
-  <si>
-    <t>6 - 9 m</t>
-  </si>
-  <si>
-    <t>6 - 12 m</t>
-  </si>
-  <si>
-    <t>18,000-45,000g/year</t>
-  </si>
-  <si>
     <t>OP-029</t>
   </si>
   <si>
@@ -931,21 +811,6 @@
     <t>OP-039</t>
   </si>
   <si>
-    <t>Casuarina equisetifolia</t>
-  </si>
-  <si>
-    <t>الكازورينا</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/X7F4g3kR/Casuarina-equisetifolia.jpg</t>
-  </si>
-  <si>
-    <t>6 - 35 m</t>
-  </si>
-  <si>
-    <t>40,000-80,000g/year</t>
-  </si>
-  <si>
     <t>OP-040</t>
   </si>
   <si>
@@ -1177,27 +1042,6 @@
     <t>OP-052</t>
   </si>
   <si>
-    <t>Zinnia elegans Jacq.</t>
-  </si>
-  <si>
-    <t>الزينيا</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/65NQpWRH/Zinnia-elegans-Jacq.jpg</t>
-  </si>
-  <si>
-    <t>0.2 - 0.4 m</t>
-  </si>
-  <si>
-    <t>200-500g/year</t>
-  </si>
-  <si>
-    <t>150-400g/year</t>
-  </si>
-  <si>
-    <t>OP-053</t>
-  </si>
-  <si>
     <t>Sansevieria trifasciata Prain</t>
   </si>
   <si>
@@ -1213,9 +1057,6 @@
     <t>400-1,200g/year</t>
   </si>
   <si>
-    <t>OP-054</t>
-  </si>
-  <si>
     <t>Tradescantia pallida</t>
   </si>
   <si>
@@ -1237,9 +1078,6 @@
     <t>400-900g/year</t>
   </si>
   <si>
-    <t>OP-055</t>
-  </si>
-  <si>
     <t>Sphagneticola trilobata</t>
   </si>
   <si>
@@ -1258,9 +1096,6 @@
     <t>800-1,500g/year</t>
   </si>
   <si>
-    <t>OP-056</t>
-  </si>
-  <si>
     <t>Lantana montevidensis</t>
   </si>
   <si>
@@ -1273,9 +1108,6 @@
     <t>1 - 2 m</t>
   </si>
   <si>
-    <t>OP-057</t>
-  </si>
-  <si>
     <t>Vachellia nilotica</t>
   </si>
   <si>
@@ -1297,9 +1129,6 @@
     <t>1,200-2,000g/year</t>
   </si>
   <si>
-    <t>OP-058</t>
-  </si>
-  <si>
     <t>Mesembryanthemum cordifolium L.f.</t>
   </si>
   <si>
@@ -1318,30 +1147,12 @@
     <t>1-4g/year</t>
   </si>
   <si>
-    <t>OP-059</t>
-  </si>
-  <si>
-    <t>Euphorbia tithymaloides</t>
-  </si>
-  <si>
-    <t>الفربيون تيثيمالويدس</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/JnQT10GQ/alfrbywn-tythymalwyds.jpg</t>
-  </si>
-  <si>
     <t>1.5 - 2.5 m</t>
   </si>
   <si>
-    <t>15-25 g/year</t>
-  </si>
-  <si>
     <t>30-50 g/year</t>
   </si>
   <si>
-    <t>OP-060</t>
-  </si>
-  <si>
     <t>Crinum asiaticum</t>
   </si>
   <si>
@@ -1360,9 +1171,6 @@
     <t>40-70 g/year</t>
   </si>
   <si>
-    <t>OP-061</t>
-  </si>
-  <si>
     <t>Volkameria inermis</t>
   </si>
   <si>
@@ -1381,9 +1189,6 @@
     <t>60-100 g/year</t>
   </si>
   <si>
-    <t>OP-062</t>
-  </si>
-  <si>
     <t>Jatropha integerrima</t>
   </si>
   <si>
@@ -1402,9 +1207,6 @@
     <t>50-80 g/year</t>
   </si>
   <si>
-    <t>OP-063</t>
-  </si>
-  <si>
     <t>Caesalpinia pulcherrima</t>
   </si>
   <si>
@@ -1556,6 +1358,33 @@
   </si>
   <si>
     <t>Portable</t>
+  </si>
+  <si>
+    <t>OP-012</t>
+  </si>
+  <si>
+    <t>OP-018</t>
+  </si>
+  <si>
+    <t>spathodea campanulata</t>
+  </si>
+  <si>
+    <t>توليب أفريقي</t>
+  </si>
+  <si>
+    <t>7 - 25 m</t>
+  </si>
+  <si>
+    <t>8 - 15 m</t>
+  </si>
+  <si>
+    <t>100,000-120,000 g/year</t>
+  </si>
+  <si>
+    <t>40,000-48,000 g/year</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/HxtvL89W/spathodea-campanulata.jpg</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1473,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1702,6 +1531,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2060,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43C3B61-471E-4868-9D01-BC7FF88A37C8}">
-  <dimension ref="A1:V186"/>
+  <dimension ref="A1:V176"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="4"/>
@@ -2151,7 +1983,7 @@
         <v>20</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>504</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
@@ -2498,35 +2330,35 @@
       <c r="A7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>76</v>
+      <c r="B7" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>79</v>
+      <c r="J7" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>31</v>
@@ -2535,7 +2367,7 @@
         <v>32</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>34</v>
@@ -2544,19 +2376,19 @@
         <v>28</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="S7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T7" t="s">
-        <v>80</v>
+      <c r="T7" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V7" s="4" t="s">
         <v>31</v>
@@ -2564,37 +2396,37 @@
     </row>
     <row r="8" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>31</v>
@@ -2609,22 +2441,22 @@
         <v>34</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T8" s="4" t="s">
-        <v>90</v>
+      <c r="T8" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="V8" s="4" t="s">
         <v>31</v>
@@ -2632,37 +2464,37 @@
     </row>
     <row r="9" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="24" t="s">
         <v>93</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>94</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>31</v>
@@ -2671,28 +2503,28 @@
         <v>32</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="V9" s="4" t="s">
         <v>31</v>
@@ -2700,37 +2532,37 @@
     </row>
     <row r="10" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>31</v>
@@ -2739,28 +2571,28 @@
         <v>32</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>91</v>
+        <v>32</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="V10" s="4" t="s">
         <v>31</v>
@@ -2768,22 +2600,22 @@
     </row>
     <row r="11" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>42</v>
@@ -2795,10 +2627,10 @@
         <v>53</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>31</v>
@@ -2810,25 +2642,25 @@
         <v>31</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>91</v>
+      <c r="T11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="V11" s="4" t="s">
         <v>31</v>
@@ -2836,22 +2668,22 @@
     </row>
     <row r="12" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>42</v>
@@ -2863,16 +2695,16 @@
         <v>53</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>31</v>
@@ -2884,19 +2716,19 @@
         <v>45</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>33</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="V12" s="4" t="s">
         <v>31</v>
@@ -2904,46 +2736,46 @@
     </row>
     <row r="13" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>115</v>
+        <v>439</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>32</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>34</v>
@@ -2955,152 +2787,152 @@
         <v>28</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T13" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="U13" s="8" t="s">
-        <v>121</v>
+        <v>28</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="4" t="s">
+      <c r="J14" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="U14" s="4" t="s">
-        <v>128</v>
+      <c r="P14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="T14" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>130</v>
+        <v>113</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="E15" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T15" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="U15" s="4" t="s">
-        <v>135</v>
+      <c r="J15" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="V15" s="4" t="s">
         <v>33</v>
@@ -3108,67 +2940,67 @@
     </row>
     <row r="16" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>137</v>
+        <v>120</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>147</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="4" t="s">
+      <c r="E16" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="U16" s="4" t="s">
-        <v>142</v>
+      <c r="J16" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="V16" s="4" t="s">
         <v>33</v>
@@ -3176,67 +3008,67 @@
     </row>
     <row r="17" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>144</v>
+        <v>121</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" s="4" t="s">
+      <c r="E17" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T17" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>149</v>
+      <c r="P17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>33</v>
@@ -3244,25 +3076,25 @@
     </row>
     <row r="18" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>28</v>
@@ -3271,10 +3103,10 @@
         <v>53</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>33</v>
@@ -3286,13 +3118,13 @@
         <v>33</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>28</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="R18" s="8" t="s">
         <v>46</v>
@@ -3301,10 +3133,10 @@
         <v>28</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="V18" s="4" t="s">
         <v>33</v>
@@ -3312,22 +3144,22 @@
     </row>
     <row r="19" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>159</v>
+        <v>440</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>42</v>
@@ -3335,32 +3167,32 @@
       <c r="H19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P19" s="8" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R19" s="8" t="s">
         <v>46</v>
@@ -3368,11 +3200,11 @@
       <c r="S19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="T19" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="U19" s="8" t="s">
-        <v>166</v>
+      <c r="T19" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="V19" s="4" t="s">
         <v>33</v>
@@ -3380,52 +3212,52 @@
     </row>
     <row r="20" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M20" s="8" t="s">
         <v>32</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q20" s="8" t="s">
         <v>45</v>
@@ -3436,11 +3268,11 @@
       <c r="S20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="T20" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="U20" s="8" t="s">
-        <v>174</v>
+      <c r="T20" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="V20" s="4" t="s">
         <v>33</v>
@@ -3448,46 +3280,46 @@
     </row>
     <row r="21" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>34</v>
@@ -3502,13 +3334,13 @@
         <v>33</v>
       </c>
       <c r="S21" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="U21" s="8" t="s">
-        <v>182</v>
+        <v>32</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="V21" s="4" t="s">
         <v>33</v>
@@ -3516,67 +3348,67 @@
     </row>
     <row r="22" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>33</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S22" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="U22" s="8" t="s">
-        <v>191</v>
+        <v>32</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="V22" s="4" t="s">
         <v>33</v>
@@ -3584,67 +3416,67 @@
     </row>
     <row r="23" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>33</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R23" s="8" t="s">
         <v>46</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="U23" s="8" t="s">
-        <v>197</v>
+        <v>32</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="V23" s="4" t="s">
         <v>33</v>
@@ -3652,90 +3484,90 @@
     </row>
     <row r="24" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>42</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="P24" s="8" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R24" s="8" t="s">
         <v>46</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>204</v>
+        <v>136</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="V24" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>42</v>
@@ -3747,10 +3579,10 @@
         <v>53</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>31</v>
@@ -3759,10 +3591,10 @@
         <v>32</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P25" s="8" t="s">
         <v>28</v>
@@ -3774,13 +3606,13 @@
         <v>46</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="V25" s="4" t="s">
         <v>33</v>
@@ -3788,52 +3620,52 @@
     </row>
     <row r="26" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="D26" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>42</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>53</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>31</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O26" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q26" s="8" t="s">
         <v>45</v>
@@ -3842,13 +3674,13 @@
         <v>46</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="V26" s="4" t="s">
         <v>33</v>
@@ -3856,22 +3688,22 @@
     </row>
     <row r="27" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>42</v>
@@ -3879,14 +3711,14 @@
       <c r="H27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>31</v>
@@ -3895,10 +3727,10 @@
         <v>32</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P27" s="8" t="s">
         <v>45</v>
@@ -3910,13 +3742,13 @@
         <v>46</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="V27" s="4" t="s">
         <v>33</v>
@@ -3924,37 +3756,37 @@
     </row>
     <row r="28" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>42</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>33</v>
@@ -3963,10 +3795,10 @@
         <v>32</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O28" s="10" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="P28" s="8" t="s">
         <v>45</v>
@@ -3975,16 +3807,16 @@
         <v>45</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="V28" s="4" t="s">
         <v>33</v>
@@ -3992,52 +3824,52 @@
     </row>
     <row r="29" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>42</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>33</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q29" s="8" t="s">
         <v>45</v>
@@ -4049,10 +3881,10 @@
         <v>32</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>204</v>
+        <v>136</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="V29" s="4" t="s">
         <v>33</v>
@@ -4060,67 +3892,67 @@
     </row>
     <row r="30" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="D30" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N30" s="8" t="s">
         <v>33</v>
       </c>
       <c r="O30" s="10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q30" s="8" t="s">
         <v>45</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S30" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="V30" s="4" t="s">
         <v>33</v>
@@ -4128,37 +3960,37 @@
     </row>
     <row r="31" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>254</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>33</v>
@@ -4170,7 +4002,7 @@
         <v>33</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P31" s="8" t="s">
         <v>28</v>
@@ -4185,54 +4017,54 @@
         <v>32</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="V31" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>262</v>
+        <v>192</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>33</v>
@@ -4241,22 +4073,22 @@
         <v>34</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q32" s="8" t="s">
         <v>45</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="S32" s="8" t="s">
         <v>32</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="V32" s="4" t="s">
         <v>33</v>
@@ -4264,67 +4096,67 @@
     </row>
     <row r="33" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>266</v>
+        <v>210</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="D33" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="8" t="s">
+      <c r="E33" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J33" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="L33" s="8" t="s">
+      <c r="J33" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R33" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R33" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="S33" s="8" t="s">
-        <v>28</v>
+      <c r="S33" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>234</v>
+        <v>274</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="V33" s="4" t="s">
         <v>33</v>
@@ -4332,67 +4164,67 @@
     </row>
     <row r="34" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>272</v>
+        <v>217</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>277</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="D34" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="U34" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R34" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="S34" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T34" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="V34" s="4" t="s">
         <v>33</v>
@@ -4400,67 +4232,67 @@
     </row>
     <row r="35" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>278</v>
+        <v>225</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="D35" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="8" t="s">
+      <c r="E35" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="10" t="s">
+      <c r="H35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="U35" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="P35" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R35" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="S35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T35" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="U35" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="V35" s="4" t="s">
         <v>33</v>
@@ -4468,67 +4300,67 @@
     </row>
     <row r="36" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>284</v>
+        <v>231</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>289</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="D36" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="10" t="s">
+      <c r="E36" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O36" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="S36" s="8" t="s">
-        <v>32</v>
+      <c r="J36" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="V36" s="4" t="s">
         <v>33</v>
@@ -4536,67 +4368,67 @@
     </row>
     <row r="37" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>291</v>
+        <v>237</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="D37" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="10" t="s">
+      <c r="E37" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J37" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="L37" s="8" t="s">
+      <c r="J37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M37" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="P37" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S37" s="8" t="s">
-        <v>28</v>
+      <c r="M37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S37" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="V37" s="4" t="s">
         <v>33</v>
@@ -4604,67 +4436,67 @@
     </row>
     <row r="38" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>296</v>
+        <v>243</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>298</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="D38" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="E38" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="10" t="s">
+      <c r="H38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J38" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M38" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R38" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="S38" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T38" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="U38" s="4" t="s">
-        <v>300</v>
+      <c r="J38" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T38" t="s">
+        <v>303</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="V38" s="4" t="s">
         <v>33</v>
@@ -4672,67 +4504,67 @@
     </row>
     <row r="39" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>302</v>
+        <v>250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>305</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="D39" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I39" s="10" t="s">
+      <c r="E39" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J39" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O39" s="10" t="s">
+      <c r="J39" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O39" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="P39" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R39" s="8" t="s">
+      <c r="P39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R39" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="S39" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="T39" s="4" t="s">
-        <v>234</v>
+      <c r="S39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T39" t="s">
+        <v>309</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="V39" s="4" t="s">
         <v>33</v>
@@ -4740,67 +4572,67 @@
     </row>
     <row r="40" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>307</v>
+        <v>255</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="D40" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="10" t="s">
+      <c r="E40" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J40" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O40" s="10" t="s">
+      <c r="J40" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O40" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="P40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R40" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="S40" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="T40" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="U40" s="4" t="s">
-        <v>312</v>
+      <c r="P40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T40" t="s">
+        <v>317</v>
+      </c>
+      <c r="U40" t="s">
+        <v>318</v>
       </c>
       <c r="V40" s="4" t="s">
         <v>33</v>
@@ -4808,67 +4640,67 @@
     </row>
     <row r="41" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>314</v>
+        <v>256</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>320</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>33</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N41" s="4" t="s">
         <v>33</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S41" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T41" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="U41" s="4" t="s">
-        <v>320</v>
+        <v>28</v>
+      </c>
+      <c r="T41" t="s">
+        <v>324</v>
+      </c>
+      <c r="U41" t="s">
+        <v>325</v>
       </c>
       <c r="V41" s="4" t="s">
         <v>33</v>
@@ -4876,37 +4708,37 @@
     </row>
     <row r="42" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>322</v>
+        <v>261</v>
+      </c>
+      <c r="B42" t="s">
+        <v>327</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>89</v>
+        <v>280</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>31</v>
@@ -4915,28 +4747,28 @@
         <v>32</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S42" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T42" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="U42" s="4" t="s">
-        <v>319</v>
+      <c r="T42" t="s">
+        <v>330</v>
+      </c>
+      <c r="U42" t="s">
+        <v>331</v>
       </c>
       <c r="V42" s="4" t="s">
         <v>33</v>
@@ -4944,25 +4776,25 @@
     </row>
     <row r="43" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>328</v>
+        <v>268</v>
+      </c>
+      <c r="B43" t="s">
+        <v>333</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="D43" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>330</v>
+      <c r="E43" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>331</v>
+        <v>41</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>32</v>
@@ -4970,11 +4802,11 @@
       <c r="I43" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="J43" t="s">
         <v>96</v>
       </c>
-      <c r="K43" s="4" t="s">
-        <v>89</v>
+      <c r="K43" t="s">
+        <v>83</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>31</v>
@@ -4992,19 +4824,19 @@
         <v>45</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="S43" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T43" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="U43" s="4" t="s">
-        <v>326</v>
+      <c r="T43" t="s">
+        <v>336</v>
+      </c>
+      <c r="U43" t="s">
+        <v>337</v>
       </c>
       <c r="V43" s="4" t="s">
         <v>33</v>
@@ -5012,25 +4844,25 @@
     </row>
     <row r="44" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>334</v>
+        <v>276</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="D44" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="15" t="s">
-        <v>336</v>
+      <c r="E44" s="12" t="s">
+        <v>340</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>26</v>
+        <v>286</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>28</v>
@@ -5038,17 +4870,17 @@
       <c r="I44" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>63</v>
+      <c r="J44" t="s">
+        <v>341</v>
+      </c>
+      <c r="K44" t="s">
+        <v>342</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>31</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N44" s="4" t="s">
         <v>33</v>
@@ -5063,16 +4895,16 @@
         <v>45</v>
       </c>
       <c r="R44" s="4" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="S44" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T44" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="U44" s="4" t="s">
-        <v>326</v>
+        <v>32</v>
+      </c>
+      <c r="T44" t="s">
+        <v>343</v>
+      </c>
+      <c r="U44" t="s">
+        <v>344</v>
       </c>
       <c r="V44" s="4" t="s">
         <v>33</v>
@@ -5080,37 +4912,37 @@
     </row>
     <row r="45" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>339</v>
+        <v>282</v>
+      </c>
+      <c r="B45" t="s">
+        <v>345</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>31</v>
@@ -5125,7 +4957,7 @@
         <v>34</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q45" s="4" t="s">
         <v>45</v>
@@ -5134,13 +4966,13 @@
         <v>33</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T45" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="U45" s="4" t="s">
-        <v>326</v>
+        <v>28</v>
+      </c>
+      <c r="T45" t="s">
+        <v>349</v>
+      </c>
+      <c r="U45" t="s">
+        <v>350</v>
       </c>
       <c r="V45" s="4" t="s">
         <v>33</v>
@@ -5148,67 +4980,67 @@
     </row>
     <row r="46" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>33</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q46" s="4" t="s">
         <v>45</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S46" s="4" t="s">
         <v>28</v>
       </c>
       <c r="T46" t="s">
-        <v>348</v>
-      </c>
-      <c r="U46" s="2" t="s">
-        <v>174</v>
+        <v>349</v>
+      </c>
+      <c r="U46" t="s">
+        <v>350</v>
       </c>
       <c r="V46" s="4" t="s">
         <v>33</v>
@@ -5216,49 +5048,49 @@
     </row>
     <row r="47" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B47" t="s">
-        <v>350</v>
+        <v>293</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>33</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="P47" s="4" t="s">
         <v>45</v>
@@ -5267,16 +5099,16 @@
         <v>45</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="T47" t="s">
-        <v>354</v>
-      </c>
-      <c r="U47" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
+      </c>
+      <c r="U47" t="s">
+        <v>361</v>
       </c>
       <c r="V47" s="4" t="s">
         <v>33</v>
@@ -5284,40 +5116,40 @@
     </row>
     <row r="48" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>297</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>362</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="D48" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>359</v>
+      <c r="E48" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>32</v>
@@ -5326,10 +5158,10 @@
         <v>33</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q48" s="4" t="s">
         <v>45</v>
@@ -5338,13 +5170,13 @@
         <v>33</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T48" t="s">
-        <v>362</v>
-      </c>
-      <c r="U48" t="s">
-        <v>363</v>
+        <v>32</v>
+      </c>
+      <c r="T48" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>367</v>
       </c>
       <c r="V48" s="4" t="s">
         <v>33</v>
@@ -5352,67 +5184,67 @@
     </row>
     <row r="49" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="D49" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="4" t="s">
+      <c r="E49" s="26" t="s">
+        <v>372</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R49" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T49" t="s">
-        <v>369</v>
-      </c>
-      <c r="U49" t="s">
-        <v>370</v>
+      <c r="J49" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="K49" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="L49" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M49" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N49" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O49" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="P49" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q49" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="R49" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S49" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="T49" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="U49" s="25" t="s">
+        <v>375</v>
       </c>
       <c r="V49" s="4" t="s">
         <v>33</v>
@@ -5420,203 +5252,203 @@
     </row>
     <row r="50" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B50" t="s">
-        <v>372</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>373</v>
-      </c>
-      <c r="D50" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="D50" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="F50" s="4" t="s">
+      <c r="E50" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="F50" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="4" t="s">
+      <c r="G50" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="J50" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L50" s="4" t="s">
+      <c r="J50" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="K50" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="L50" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="M50" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O50" s="4" t="s">
+      <c r="M50" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N50" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O50" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="P50" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q50" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R50" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S50" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T50" t="s">
-        <v>375</v>
-      </c>
-      <c r="U50" t="s">
-        <v>376</v>
+      <c r="P50" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q50" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="R50" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S50" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="T50" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="U50" s="25" t="s">
+        <v>381</v>
       </c>
       <c r="V50" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="B51" t="s">
-        <v>378</v>
+        <v>319</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>382</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="D51" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="D51" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="4" t="s">
+      <c r="E51" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I51" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="L51" s="4" t="s">
+      <c r="J51" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="K51" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="L51" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="M51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" s="4" t="s">
+      <c r="M51" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="O51" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q51" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="R51" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="S51" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="T51" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="U51" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="V51" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>437</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="J52" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="K52" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="L52" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="O51" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q51" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R51" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T51" t="s">
-        <v>382</v>
-      </c>
-      <c r="U51" t="s">
-        <v>383</v>
-      </c>
-      <c r="V51" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="B52" t="s">
-        <v>385</v>
-      </c>
-      <c r="C52" s="24" t="s">
+      <c r="M52" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O52" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P52" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q52" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="R52" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S52" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="T52" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="12" t="s">
+      <c r="U52" s="25" t="s">
         <v>387</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J52" t="s">
-        <v>102</v>
-      </c>
-      <c r="K52" t="s">
-        <v>89</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q52" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R52" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T52" t="s">
-        <v>388</v>
-      </c>
-      <c r="U52" t="s">
-        <v>389</v>
       </c>
       <c r="V52" s="4" t="s">
         <v>33</v>
@@ -5624,684 +5456,78 @@
     </row>
     <row r="53" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>24</v>
+        <v>332</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>442</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="I53" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="J53" t="s">
-        <v>394</v>
-      </c>
-      <c r="K53" t="s">
-        <v>395</v>
-      </c>
-      <c r="L53" s="4" t="s">
+      <c r="J53" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="K53" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="L53" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M53" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N53" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="O53" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="P53" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q53" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="R53" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="S53" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="T53" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="U53" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="V53" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O53" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q53" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R53" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T53" t="s">
-        <v>396</v>
-      </c>
-      <c r="U53" t="s">
-        <v>397</v>
-      </c>
-      <c r="V53" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="B54" t="s">
-        <v>399</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>400</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M54" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N54" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O54" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q54" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R54" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S54" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T54" t="s">
-        <v>403</v>
-      </c>
-      <c r="U54" t="s">
-        <v>404</v>
-      </c>
-      <c r="V54" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O55" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q55" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R55" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S55" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T55" t="s">
-        <v>403</v>
-      </c>
-      <c r="U55" t="s">
-        <v>404</v>
-      </c>
-      <c r="V55" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N56" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O56" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R56" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S56" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T56" t="s">
-        <v>416</v>
-      </c>
-      <c r="U56" t="s">
-        <v>417</v>
-      </c>
-      <c r="V56" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q57" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R57" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S57" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T57" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="U57" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="V57" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="25" t="s">
-        <v>425</v>
-      </c>
-      <c r="B58" s="25" t="s">
-        <v>426</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="F58" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="G58" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="J58" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="K58" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="L58" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="M58" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="N58" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="O58" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P58" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q58" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="R58" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="S58" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="T58" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="U58" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="V58" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="B59" s="25" t="s">
-        <v>433</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="F59" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H59" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I59" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="J59" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="K59" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="L59" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="M59" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="N59" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="O59" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="P59" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q59" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="R59" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="S59" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="T59" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="U59" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="V59" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>440</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>441</v>
-      </c>
-      <c r="D60" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="26" t="s">
-        <v>442</v>
-      </c>
-      <c r="F60" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G60" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H60" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I60" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="K60" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="L60" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="M60" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="N60" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="O60" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P60" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q60" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="R60" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="S60" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="T60" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="U60" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="V60" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="24" t="s">
-        <v>446</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="27" t="s">
-        <v>449</v>
-      </c>
-      <c r="F61" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="G61" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I61" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="J61" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="K61" s="24" t="s">
-        <v>429</v>
-      </c>
-      <c r="L61" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="M61" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="O61" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="P61" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q61" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="R61" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="S61" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="T61" s="24" t="s">
-        <v>451</v>
-      </c>
-      <c r="U61" s="24" t="s">
-        <v>452</v>
-      </c>
-      <c r="V61" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="25" t="s">
-        <v>453</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>454</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>455</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="F62" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G62" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H62" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>450</v>
-      </c>
-      <c r="K62" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="L62" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="M62" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="O62" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="P62" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q62" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="R62" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="S62" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="T62" s="25" t="s">
-        <v>451</v>
-      </c>
-      <c r="U62" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="V62" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
+    </row>
+    <row r="54" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="55" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="63" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="65" ht="14.5" x14ac:dyDescent="0.35"/>
@@ -6416,33 +5642,23 @@
     <row r="174" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="175" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="176" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U45">
-    <sortCondition ref="A2:A45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U37">
+    <sortCondition ref="A2:A37"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B26:B43 B1:B18 B45:B46 B55:B60 B63:B1048576">
+  <conditionalFormatting sqref="B53:B1048576 B46:B50 B37:B38 B20:B35 B1:B14">
     <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61:B62">
+  <conditionalFormatting sqref="B51:B52">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{58D66573-3890-4498-A66F-3227660DC8D7}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M18 S2:S1048576 P2:Q1048576 H2:H1048576 M26:M1048576" xr:uid="{26BEA281-5615-4C1E-80B9-785C1C126E1E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M14 M20:M1048576 S2:S1048576 P2:Q1048576 H2:H1048576" xr:uid="{26BEA281-5615-4C1E-80B9-785C1C126E1E}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L18 N2:N1048576 L26:L1048576 V2:V1048576" xr:uid="{BADEB7D1-F197-43A2-9AAB-F8E1A586A330}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L14 L20:L1048576 N2:N1048576 V2:V1048576" xr:uid="{BADEB7D1-F197-43A2-9AAB-F8E1A586A330}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{9B94FA55-E999-447C-AE3A-D83167D0511E}">
@@ -6466,125 +5682,106 @@
     <hyperlink ref="D3" r:id="rId2" xr:uid="{5323DA1F-90E3-4EC4-9236-3FABF03E7B7B}"/>
     <hyperlink ref="D4" r:id="rId3" xr:uid="{018E3A31-D699-48D2-AD40-1BB7690AEFD7}"/>
     <hyperlink ref="D5" r:id="rId4" xr:uid="{392A5314-B9BB-4171-8F94-222188BA99B0}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{C2587916-F827-41B7-8EDB-D66AF039E12E}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{5B092A59-B505-409F-881F-B73548F6938E}"/>
-    <hyperlink ref="D9" r:id="rId7" xr:uid="{000CFFF4-9940-48FD-A423-432D48721CE1}"/>
-    <hyperlink ref="D10" r:id="rId8" xr:uid="{3CA9DF8A-4187-4A78-B778-6207A316B333}"/>
-    <hyperlink ref="D11" r:id="rId9" xr:uid="{0E189887-694C-422E-A29F-FCEF22C7419F}"/>
-    <hyperlink ref="D12" r:id="rId10" xr:uid="{8C60A978-0633-4E7B-9B20-39535DD7DDC8}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{719CD489-BB63-497E-AE08-21DC9CA54CA3}"/>
-    <hyperlink ref="D14" r:id="rId12" xr:uid="{DF2B3021-CB8F-44D8-BD31-AA8794C176EC}"/>
-    <hyperlink ref="D15" r:id="rId13" xr:uid="{D7DA4A7E-52AB-4E28-B3FC-EF963D4DDD4D}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{1C616BAB-4C73-4EBF-B776-7BA076A7033C}"/>
-    <hyperlink ref="D17" r:id="rId15" xr:uid="{23CE6F16-08A6-4E8D-9C4D-C9B5127E144A}"/>
-    <hyperlink ref="D18" r:id="rId16" xr:uid="{ECBD96C7-2596-4362-B615-FF5B44F512E6}"/>
-    <hyperlink ref="D19" r:id="rId17" xr:uid="{4101BD30-6698-4EB1-8903-7E1FFBFB9B63}"/>
-    <hyperlink ref="D20" r:id="rId18" xr:uid="{4874A1A2-8C4B-4BED-8969-BE02721678F3}"/>
-    <hyperlink ref="D21" r:id="rId19" xr:uid="{2252DC4A-0C0B-416E-BC31-B768BCEAE16F}"/>
-    <hyperlink ref="D22" r:id="rId20" xr:uid="{4112E39B-C26E-46CC-A777-150B9CFB739F}"/>
-    <hyperlink ref="D23" r:id="rId21" xr:uid="{1EAE0336-600F-4BB9-896A-74726C93DF17}"/>
-    <hyperlink ref="D24" r:id="rId22" xr:uid="{21F64656-BD08-4D53-8965-D64438F9240D}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{3C3C0EB3-86DF-4285-8FCA-00C307A1F95B}"/>
-    <hyperlink ref="D26" r:id="rId24" xr:uid="{B18E89B5-8326-4B91-9453-371E52799A2B}"/>
-    <hyperlink ref="D27" r:id="rId25" xr:uid="{0065F6AA-32BB-4DC3-AA2B-7BCDD6A44EBB}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{1D7D50F0-D5C5-4C40-A96A-49B41DE78C68}"/>
-    <hyperlink ref="D29" r:id="rId27" xr:uid="{E9386162-3288-47F3-A64B-B7C674CF0CD6}"/>
-    <hyperlink ref="D30" r:id="rId28" xr:uid="{CBFB0E77-BEDF-48EA-9924-465E247355C4}"/>
-    <hyperlink ref="D31" r:id="rId29" xr:uid="{7044A41C-3685-470B-8F5B-80661D43C5E2}"/>
-    <hyperlink ref="D32" r:id="rId30" xr:uid="{9D6A02AB-3D8C-4EB2-9FAA-84914A73B229}"/>
-    <hyperlink ref="D33" r:id="rId31" xr:uid="{9CABA5BB-A509-4C32-89C4-9B32A2504DF8}"/>
-    <hyperlink ref="D34" r:id="rId32" xr:uid="{5A417341-CE47-428C-AE6B-8D0346B9AE99}"/>
-    <hyperlink ref="D35" r:id="rId33" xr:uid="{CF17741F-78A9-4737-A2EB-92996670749C}"/>
-    <hyperlink ref="D36" r:id="rId34" xr:uid="{06CB0C63-7DAC-491B-B517-7A7458705E0C}"/>
-    <hyperlink ref="D37" r:id="rId35" xr:uid="{1309698B-F196-45BB-9281-74166A20313B}"/>
-    <hyperlink ref="D38" r:id="rId36" xr:uid="{7876597A-46B3-4B6F-A74A-403496DE329B}"/>
-    <hyperlink ref="D39" r:id="rId37" xr:uid="{958469ED-DB41-484F-A776-1929CD714AF0}"/>
-    <hyperlink ref="D40" r:id="rId38" xr:uid="{794C1888-69A6-447B-A567-A33FE86DF71D}"/>
-    <hyperlink ref="D41" r:id="rId39" xr:uid="{FEC534E3-9431-492F-BD28-606DCB57CC8B}"/>
-    <hyperlink ref="D42" r:id="rId40" xr:uid="{2FB904E2-A75D-4A26-89C5-7589D678E56D}"/>
-    <hyperlink ref="D43" r:id="rId41" xr:uid="{BF526CAA-01FF-4066-91C6-A6F8BB3FCE21}"/>
-    <hyperlink ref="D44" r:id="rId42" xr:uid="{564ECDC1-2645-4F7E-98E6-1AABE34BEBC5}"/>
-    <hyperlink ref="D45" r:id="rId43" xr:uid="{FDCBB645-209E-4F77-ACEA-005347D2AE33}"/>
-    <hyperlink ref="E45" r:id="rId44" xr:uid="{54BE221F-8340-430F-949D-BE5DE2FA3C4E}"/>
-    <hyperlink ref="E44" r:id="rId45" xr:uid="{A942DD69-E44F-4CB0-B16D-4BADC06684CA}"/>
-    <hyperlink ref="E43" r:id="rId46" xr:uid="{5E7FC22A-71EE-428D-811A-20CD14846773}"/>
-    <hyperlink ref="E42" r:id="rId47" xr:uid="{C81E3ED7-E859-4259-8AF6-E7FC262BB034}"/>
-    <hyperlink ref="E41" r:id="rId48" xr:uid="{911FC1D7-A9ED-4554-916C-71358693FDB0}"/>
-    <hyperlink ref="D7" r:id="rId49" xr:uid="{9DAD28EA-4D30-4C83-907D-B7839F214B5C}"/>
-    <hyperlink ref="D46:D54" r:id="rId50" display="Open Image" xr:uid="{FD9F38CB-4E6C-4DD2-80EE-848175CFCA26}"/>
-    <hyperlink ref="D55" r:id="rId51" xr:uid="{6B895142-1E73-4D31-AAC6-1CE3C4CB9B68}"/>
-    <hyperlink ref="D56" r:id="rId52" xr:uid="{91615C1B-C881-4716-A52E-40DD942077BD}"/>
-    <hyperlink ref="D46" r:id="rId53" xr:uid="{3377DCFF-475F-4542-93FD-6062E02F5E45}"/>
-    <hyperlink ref="D47" r:id="rId54" xr:uid="{12139F7E-B38E-437B-9222-336AF9D313FF}"/>
-    <hyperlink ref="D48" r:id="rId55" xr:uid="{CC1893E0-7383-4D0F-B2FE-CFA7DBAE0BBE}"/>
-    <hyperlink ref="D49" r:id="rId56" xr:uid="{94FD7C65-6909-4A50-AD27-24EDD09433A8}"/>
-    <hyperlink ref="D50" r:id="rId57" xr:uid="{E845C3E1-366F-42A8-A577-9E93944ED709}"/>
-    <hyperlink ref="D51" r:id="rId58" xr:uid="{C489F4DF-E77E-4E9B-BB14-5119A4FD9738}"/>
-    <hyperlink ref="D52" r:id="rId59" xr:uid="{575FEEB6-B9F7-4106-8B3F-F80429460924}"/>
-    <hyperlink ref="D53" r:id="rId60" xr:uid="{8ECF9E2D-3F0A-4F42-AEBB-DE9451488D6E}"/>
-    <hyperlink ref="D54" r:id="rId61" xr:uid="{BDD4B0CC-0287-42D5-AE5A-3CC11C4612A6}"/>
-    <hyperlink ref="E46" r:id="rId62" xr:uid="{3CD73538-0D5C-4762-9F07-5D755DDEAF16}"/>
-    <hyperlink ref="E47" r:id="rId63" xr:uid="{40FF8D89-9B78-411F-8DB4-626B9AFF5A1D}"/>
-    <hyperlink ref="E48" r:id="rId64" xr:uid="{CA1C7212-1B59-4F8C-8BD6-3636D3D60A6A}"/>
-    <hyperlink ref="E49" r:id="rId65" xr:uid="{D38263CB-493C-439F-9F17-4236A96C66D1}"/>
-    <hyperlink ref="E50" r:id="rId66" xr:uid="{EF268AAA-D055-4ABB-9D80-BF7100CCE5F6}"/>
-    <hyperlink ref="E51" r:id="rId67" xr:uid="{9510EADC-FE45-4655-A213-003980F89284}"/>
-    <hyperlink ref="E52" r:id="rId68" xr:uid="{F8417B3D-8E2F-49A0-9346-F7DD1246A5EF}"/>
-    <hyperlink ref="E53" r:id="rId69" xr:uid="{784F421E-E918-4DD5-B45B-D31C95BEA044}"/>
-    <hyperlink ref="E54" r:id="rId70" xr:uid="{E1623873-15FE-460E-A915-DCDFCC91D3DA}"/>
-    <hyperlink ref="E55" r:id="rId71" xr:uid="{1A559C67-3450-466A-BFBC-07027D6BBCF5}"/>
-    <hyperlink ref="E56" r:id="rId72" xr:uid="{FA985005-458A-41F1-8F52-FF06E87B4865}"/>
-    <hyperlink ref="E40" r:id="rId73" xr:uid="{F038B75C-7931-42AD-9969-6CD70B6EC772}"/>
-    <hyperlink ref="E39" r:id="rId74" xr:uid="{84FC8343-E3AA-4D3A-BB39-83E0BFE9B563}"/>
-    <hyperlink ref="E38" r:id="rId75" xr:uid="{B2C56123-0097-4CCC-AF7B-A2DE5F633E15}"/>
-    <hyperlink ref="E36" r:id="rId76" xr:uid="{11AFD464-CA0C-4AB6-A72C-328EF8CF24ED}"/>
-    <hyperlink ref="E35" r:id="rId77" xr:uid="{5A6AFE26-9F39-46A3-A100-193A48287A3F}"/>
-    <hyperlink ref="E34" r:id="rId78" xr:uid="{DDB837BA-3D81-41EA-9139-B2979B5F07EB}"/>
-    <hyperlink ref="E33" r:id="rId79" xr:uid="{DBA6C7E9-CD5E-40DC-A123-2FCC71D0FB48}"/>
-    <hyperlink ref="E24" r:id="rId80" xr:uid="{12ACB02F-48ED-4EE0-9507-EC61696A7FA3}"/>
-    <hyperlink ref="E25" r:id="rId81" xr:uid="{5C50D50C-3B59-4219-9D58-CB56E8E4D83D}"/>
-    <hyperlink ref="E27" r:id="rId82" xr:uid="{A263D1F2-CC83-4D4E-B6AA-B01AA7A310EB}"/>
-    <hyperlink ref="E28" r:id="rId83" xr:uid="{2F9757A9-9D79-4515-96E4-E4F3DBC74C11}"/>
-    <hyperlink ref="E29" r:id="rId84" xr:uid="{F4511DE4-AE2D-442C-B19E-D21562864BE5}"/>
-    <hyperlink ref="E30" r:id="rId85" xr:uid="{6BDC74CA-B98A-4E3C-BE2B-5014BF208EC5}"/>
-    <hyperlink ref="E31" r:id="rId86" xr:uid="{DBCA2FA0-F5E4-4B17-9D87-8CC3A5D53F8D}"/>
-    <hyperlink ref="E32" r:id="rId87" xr:uid="{ABC699BF-9AEF-4876-A7E0-2587D1E9EAC0}"/>
-    <hyperlink ref="E2" r:id="rId88" xr:uid="{DA9FB63F-9F74-435C-B5D8-06A21ED3558C}"/>
-    <hyperlink ref="E3" r:id="rId89" xr:uid="{4BE46902-2799-42A9-9C90-0CCEE6252939}"/>
-    <hyperlink ref="E4" r:id="rId90" xr:uid="{8FCD70DA-9DCA-468F-AA3E-53987C024760}"/>
-    <hyperlink ref="E5" r:id="rId91" xr:uid="{E844596D-F0CD-407D-BEA4-453A5F4E279C}"/>
-    <hyperlink ref="E6" r:id="rId92" xr:uid="{38F1636E-04EF-45FA-A853-30396B0673BC}"/>
-    <hyperlink ref="E7" r:id="rId93" xr:uid="{3165D5FD-C390-4891-AFEF-1A038F336C20}"/>
-    <hyperlink ref="E8" r:id="rId94" xr:uid="{FCC9E8ED-A3E7-4095-AFE1-27D2DC670279}"/>
-    <hyperlink ref="E9" r:id="rId95" xr:uid="{107532CA-5743-406B-95B9-68ECDC90423E}"/>
-    <hyperlink ref="E10" r:id="rId96" xr:uid="{BB486086-2D95-4F5D-BA89-5641639117FF}"/>
-    <hyperlink ref="E11" r:id="rId97" xr:uid="{A7B283C4-7CC9-45DA-BEA9-C4B723BA0901}"/>
-    <hyperlink ref="E12" r:id="rId98" xr:uid="{322CF00C-EA10-456A-B798-E9038EF2F98E}"/>
-    <hyperlink ref="E13" r:id="rId99" xr:uid="{A5F34439-5B1F-484F-926B-9E881979CA2E}"/>
-    <hyperlink ref="E14" r:id="rId100" xr:uid="{13F387A6-F110-4670-A23B-D5BD4882CBC5}"/>
-    <hyperlink ref="E15" r:id="rId101" xr:uid="{B06AC7C1-2925-4A6E-BBDD-686E6460F34D}"/>
-    <hyperlink ref="E16" r:id="rId102" xr:uid="{88DEB030-5BCA-4AC4-9C4C-9F00355F866F}"/>
-    <hyperlink ref="E17" r:id="rId103" xr:uid="{F7C4CC7F-176E-4169-9057-340E4EC0B6F7}"/>
-    <hyperlink ref="E18" r:id="rId104" xr:uid="{FA76E78D-5E89-42F7-AC4E-E641F9E26B7A}"/>
-    <hyperlink ref="E19" r:id="rId105" xr:uid="{10716D52-5753-4C47-A7F2-CDD8599B36C1}"/>
-    <hyperlink ref="E20" r:id="rId106" xr:uid="{A818F6D6-B899-4855-B989-FBB6827669A9}"/>
-    <hyperlink ref="E21" r:id="rId107" xr:uid="{12F92AB0-9F69-4935-B4D4-D20F8DE0D7E1}"/>
-    <hyperlink ref="E22" r:id="rId108" xr:uid="{FD67F12F-1173-4E4B-A8E3-F3A81C85E4EB}"/>
-    <hyperlink ref="E23" r:id="rId109" xr:uid="{64CA3CAB-0D61-45C4-9B27-C04EE14B58B5}"/>
-    <hyperlink ref="E26" r:id="rId110" xr:uid="{335A8E87-D725-4028-9DB7-E8624E6E544C}"/>
-    <hyperlink ref="E37" r:id="rId111" xr:uid="{B9227BF6-565E-4CC0-BF4C-4C508A7DB46B}"/>
-    <hyperlink ref="D57" r:id="rId112" xr:uid="{B6DDFCF8-2D59-4DA8-9C7A-A1B7B7E26168}"/>
-    <hyperlink ref="E57" r:id="rId113" xr:uid="{42C95BBC-98B4-4E80-B097-88E6F392B903}"/>
-    <hyperlink ref="E58" r:id="rId114" xr:uid="{4F00AB62-1372-499A-8211-9711806AABEA}"/>
-    <hyperlink ref="E59" r:id="rId115" xr:uid="{F708A31D-C2B5-4330-AF9A-C16DA58EC2AE}"/>
-    <hyperlink ref="E60" r:id="rId116" xr:uid="{14D81D35-D16E-4182-94FC-43E955C1B5D3}"/>
-    <hyperlink ref="E62" r:id="rId117" xr:uid="{21CE0160-5815-4046-B128-41F3EA044403}"/>
-    <hyperlink ref="E61" r:id="rId118" xr:uid="{F770A038-8037-436F-BBC3-A69F7E24E474}"/>
-    <hyperlink ref="D58" r:id="rId119" xr:uid="{A040D01A-9239-4B6F-9744-25BAB54B8B06}"/>
-    <hyperlink ref="D59" r:id="rId120" xr:uid="{2E14643C-EFD7-4CD4-942A-E4238BD95F13}"/>
-    <hyperlink ref="D60" r:id="rId121" xr:uid="{41E06457-0D18-46A5-944D-698E40BE79B1}"/>
-    <hyperlink ref="D61" r:id="rId122" xr:uid="{1F4339E4-23FD-4F71-A2D7-B9A63D2168DC}"/>
-    <hyperlink ref="D62" r:id="rId123" xr:uid="{74C61858-AB0D-40D4-826E-206B16E6BE95}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{5B092A59-B505-409F-881F-B73548F6938E}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{000CFFF4-9940-48FD-A423-432D48721CE1}"/>
+    <hyperlink ref="D9" r:id="rId7" xr:uid="{3CA9DF8A-4187-4A78-B778-6207A316B333}"/>
+    <hyperlink ref="D10" r:id="rId8" xr:uid="{0E189887-694C-422E-A29F-FCEF22C7419F}"/>
+    <hyperlink ref="D11" r:id="rId9" xr:uid="{719CD489-BB63-497E-AE08-21DC9CA54CA3}"/>
+    <hyperlink ref="D12" r:id="rId10" xr:uid="{DF2B3021-CB8F-44D8-BD31-AA8794C176EC}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{23CE6F16-08A6-4E8D-9C4D-C9B5127E144A}"/>
+    <hyperlink ref="D14" r:id="rId12" xr:uid="{ECBD96C7-2596-4362-B615-FF5B44F512E6}"/>
+    <hyperlink ref="D15" r:id="rId13" xr:uid="{4101BD30-6698-4EB1-8903-7E1FFBFB9B63}"/>
+    <hyperlink ref="D16" r:id="rId14" xr:uid="{4874A1A2-8C4B-4BED-8969-BE02721678F3}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{2252DC4A-0C0B-416E-BC31-B768BCEAE16F}"/>
+    <hyperlink ref="D18" r:id="rId16" xr:uid="{1EAE0336-600F-4BB9-896A-74726C93DF17}"/>
+    <hyperlink ref="D19" r:id="rId17" xr:uid="{3C3C0EB3-86DF-4285-8FCA-00C307A1F95B}"/>
+    <hyperlink ref="D20" r:id="rId18" xr:uid="{B18E89B5-8326-4B91-9453-371E52799A2B}"/>
+    <hyperlink ref="D21" r:id="rId19" xr:uid="{1D7D50F0-D5C5-4C40-A96A-49B41DE78C68}"/>
+    <hyperlink ref="D22" r:id="rId20" xr:uid="{E9386162-3288-47F3-A64B-B7C674CF0CD6}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{CBFB0E77-BEDF-48EA-9924-465E247355C4}"/>
+    <hyperlink ref="D24" r:id="rId22" xr:uid="{7044A41C-3685-470B-8F5B-80661D43C5E2}"/>
+    <hyperlink ref="D25" r:id="rId23" xr:uid="{9D6A02AB-3D8C-4EB2-9FAA-84914A73B229}"/>
+    <hyperlink ref="D26" r:id="rId24" xr:uid="{9CABA5BB-A509-4C32-89C4-9B32A2504DF8}"/>
+    <hyperlink ref="D27" r:id="rId25" xr:uid="{5A417341-CE47-428C-AE6B-8D0346B9AE99}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{CF17741F-78A9-4737-A2EB-92996670749C}"/>
+    <hyperlink ref="D29" r:id="rId27" xr:uid="{06CB0C63-7DAC-491B-B517-7A7458705E0C}"/>
+    <hyperlink ref="D30" r:id="rId28" xr:uid="{1309698B-F196-45BB-9281-74166A20313B}"/>
+    <hyperlink ref="D31" r:id="rId29" xr:uid="{958469ED-DB41-484F-A776-1929CD714AF0}"/>
+    <hyperlink ref="D32" r:id="rId30" xr:uid="{794C1888-69A6-447B-A567-A33FE86DF71D}"/>
+    <hyperlink ref="D33" r:id="rId31" xr:uid="{FEC534E3-9431-492F-BD28-606DCB57CC8B}"/>
+    <hyperlink ref="D34" r:id="rId32" xr:uid="{2FB904E2-A75D-4A26-89C5-7589D678E56D}"/>
+    <hyperlink ref="D35" r:id="rId33" xr:uid="{BF526CAA-01FF-4066-91C6-A6F8BB3FCE21}"/>
+    <hyperlink ref="D36" r:id="rId34" xr:uid="{564ECDC1-2645-4F7E-98E6-1AABE34BEBC5}"/>
+    <hyperlink ref="D37" r:id="rId35" xr:uid="{FDCBB645-209E-4F77-ACEA-005347D2AE33}"/>
+    <hyperlink ref="E37" r:id="rId36" xr:uid="{54BE221F-8340-430F-949D-BE5DE2FA3C4E}"/>
+    <hyperlink ref="E36" r:id="rId37" xr:uid="{A942DD69-E44F-4CB0-B16D-4BADC06684CA}"/>
+    <hyperlink ref="E35" r:id="rId38" xr:uid="{5E7FC22A-71EE-428D-811A-20CD14846773}"/>
+    <hyperlink ref="E34" r:id="rId39" xr:uid="{C81E3ED7-E859-4259-8AF6-E7FC262BB034}"/>
+    <hyperlink ref="E33" r:id="rId40" xr:uid="{911FC1D7-A9ED-4554-916C-71358693FDB0}"/>
+    <hyperlink ref="D38:D45" r:id="rId41" display="Open Image" xr:uid="{FD9F38CB-4E6C-4DD2-80EE-848175CFCA26}"/>
+    <hyperlink ref="D46" r:id="rId42" xr:uid="{6B895142-1E73-4D31-AAC6-1CE3C4CB9B68}"/>
+    <hyperlink ref="D47" r:id="rId43" xr:uid="{91615C1B-C881-4716-A52E-40DD942077BD}"/>
+    <hyperlink ref="D38" r:id="rId44" xr:uid="{3377DCFF-475F-4542-93FD-6062E02F5E45}"/>
+    <hyperlink ref="D39" r:id="rId45" xr:uid="{12139F7E-B38E-437B-9222-336AF9D313FF}"/>
+    <hyperlink ref="D40" r:id="rId46" xr:uid="{CC1893E0-7383-4D0F-B2FE-CFA7DBAE0BBE}"/>
+    <hyperlink ref="D41" r:id="rId47" xr:uid="{94FD7C65-6909-4A50-AD27-24EDD09433A8}"/>
+    <hyperlink ref="D42" r:id="rId48" xr:uid="{E845C3E1-366F-42A8-A577-9E93944ED709}"/>
+    <hyperlink ref="D43" r:id="rId49" xr:uid="{575FEEB6-B9F7-4106-8B3F-F80429460924}"/>
+    <hyperlink ref="D44" r:id="rId50" xr:uid="{8ECF9E2D-3F0A-4F42-AEBB-DE9451488D6E}"/>
+    <hyperlink ref="D45" r:id="rId51" xr:uid="{BDD4B0CC-0287-42D5-AE5A-3CC11C4612A6}"/>
+    <hyperlink ref="E38" r:id="rId52" xr:uid="{3CD73538-0D5C-4762-9F07-5D755DDEAF16}"/>
+    <hyperlink ref="E39" r:id="rId53" xr:uid="{40FF8D89-9B78-411F-8DB4-626B9AFF5A1D}"/>
+    <hyperlink ref="E40" r:id="rId54" xr:uid="{CA1C7212-1B59-4F8C-8BD6-3636D3D60A6A}"/>
+    <hyperlink ref="E41" r:id="rId55" xr:uid="{D38263CB-493C-439F-9F17-4236A96C66D1}"/>
+    <hyperlink ref="E42" r:id="rId56" xr:uid="{EF268AAA-D055-4ABB-9D80-BF7100CCE5F6}"/>
+    <hyperlink ref="E43" r:id="rId57" xr:uid="{F8417B3D-8E2F-49A0-9346-F7DD1246A5EF}"/>
+    <hyperlink ref="E44" r:id="rId58" xr:uid="{784F421E-E918-4DD5-B45B-D31C95BEA044}"/>
+    <hyperlink ref="E45" r:id="rId59" xr:uid="{E1623873-15FE-460E-A915-DCDFCC91D3DA}"/>
+    <hyperlink ref="E46" r:id="rId60" xr:uid="{1A559C67-3450-466A-BFBC-07027D6BBCF5}"/>
+    <hyperlink ref="E47" r:id="rId61" xr:uid="{FA985005-458A-41F1-8F52-FF06E87B4865}"/>
+    <hyperlink ref="E32" r:id="rId62" xr:uid="{F038B75C-7931-42AD-9969-6CD70B6EC772}"/>
+    <hyperlink ref="E31" r:id="rId63" xr:uid="{84FC8343-E3AA-4D3A-BB39-83E0BFE9B563}"/>
+    <hyperlink ref="E29" r:id="rId64" xr:uid="{11AFD464-CA0C-4AB6-A72C-328EF8CF24ED}"/>
+    <hyperlink ref="E28" r:id="rId65" xr:uid="{5A6AFE26-9F39-46A3-A100-193A48287A3F}"/>
+    <hyperlink ref="E27" r:id="rId66" xr:uid="{DDB837BA-3D81-41EA-9139-B2979B5F07EB}"/>
+    <hyperlink ref="E26" r:id="rId67" xr:uid="{DBA6C7E9-CD5E-40DC-A123-2FCC71D0FB48}"/>
+    <hyperlink ref="E19" r:id="rId68" xr:uid="{5C50D50C-3B59-4219-9D58-CB56E8E4D83D}"/>
+    <hyperlink ref="E21" r:id="rId69" xr:uid="{2F9757A9-9D79-4515-96E4-E4F3DBC74C11}"/>
+    <hyperlink ref="E22" r:id="rId70" xr:uid="{F4511DE4-AE2D-442C-B19E-D21562864BE5}"/>
+    <hyperlink ref="E23" r:id="rId71" xr:uid="{6BDC74CA-B98A-4E3C-BE2B-5014BF208EC5}"/>
+    <hyperlink ref="E24" r:id="rId72" xr:uid="{DBCA2FA0-F5E4-4B17-9D87-8CC3A5D53F8D}"/>
+    <hyperlink ref="E25" r:id="rId73" xr:uid="{ABC699BF-9AEF-4876-A7E0-2587D1E9EAC0}"/>
+    <hyperlink ref="E2" r:id="rId74" xr:uid="{DA9FB63F-9F74-435C-B5D8-06A21ED3558C}"/>
+    <hyperlink ref="E3" r:id="rId75" xr:uid="{4BE46902-2799-42A9-9C90-0CCEE6252939}"/>
+    <hyperlink ref="E4" r:id="rId76" xr:uid="{8FCD70DA-9DCA-468F-AA3E-53987C024760}"/>
+    <hyperlink ref="E5" r:id="rId77" xr:uid="{E844596D-F0CD-407D-BEA4-453A5F4E279C}"/>
+    <hyperlink ref="E7" r:id="rId78" xr:uid="{FCC9E8ED-A3E7-4095-AFE1-27D2DC670279}"/>
+    <hyperlink ref="E8" r:id="rId79" xr:uid="{107532CA-5743-406B-95B9-68ECDC90423E}"/>
+    <hyperlink ref="E9" r:id="rId80" xr:uid="{BB486086-2D95-4F5D-BA89-5641639117FF}"/>
+    <hyperlink ref="E10" r:id="rId81" xr:uid="{A7B283C4-7CC9-45DA-BEA9-C4B723BA0901}"/>
+    <hyperlink ref="E11" r:id="rId82" xr:uid="{A5F34439-5B1F-484F-926B-9E881979CA2E}"/>
+    <hyperlink ref="E12" r:id="rId83" xr:uid="{13F387A6-F110-4670-A23B-D5BD4882CBC5}"/>
+    <hyperlink ref="E13" r:id="rId84" xr:uid="{F7C4CC7F-176E-4169-9057-340E4EC0B6F7}"/>
+    <hyperlink ref="E14" r:id="rId85" xr:uid="{FA76E78D-5E89-42F7-AC4E-E641F9E26B7A}"/>
+    <hyperlink ref="E15" r:id="rId86" xr:uid="{10716D52-5753-4C47-A7F2-CDD8599B36C1}"/>
+    <hyperlink ref="E16" r:id="rId87" xr:uid="{A818F6D6-B899-4855-B989-FBB6827669A9}"/>
+    <hyperlink ref="E17" r:id="rId88" xr:uid="{12F92AB0-9F69-4935-B4D4-D20F8DE0D7E1}"/>
+    <hyperlink ref="E18" r:id="rId89" xr:uid="{64CA3CAB-0D61-45C4-9B27-C04EE14B58B5}"/>
+    <hyperlink ref="E20" r:id="rId90" xr:uid="{335A8E87-D725-4028-9DB7-E8624E6E544C}"/>
+    <hyperlink ref="E30" r:id="rId91" xr:uid="{B9227BF6-565E-4CC0-BF4C-4C508A7DB46B}"/>
+    <hyperlink ref="D48" r:id="rId92" xr:uid="{B6DDFCF8-2D59-4DA8-9C7A-A1B7B7E26168}"/>
+    <hyperlink ref="E48" r:id="rId93" xr:uid="{42C95BBC-98B4-4E80-B097-88E6F392B903}"/>
+    <hyperlink ref="E49" r:id="rId94" xr:uid="{F708A31D-C2B5-4330-AF9A-C16DA58EC2AE}"/>
+    <hyperlink ref="E50" r:id="rId95" xr:uid="{14D81D35-D16E-4182-94FC-43E955C1B5D3}"/>
+    <hyperlink ref="E52" r:id="rId96" xr:uid="{21CE0160-5815-4046-B128-41F3EA044403}"/>
+    <hyperlink ref="E51" r:id="rId97" xr:uid="{F770A038-8037-436F-BBC3-A69F7E24E474}"/>
+    <hyperlink ref="D49" r:id="rId98" xr:uid="{2E14643C-EFD7-4CD4-942A-E4238BD95F13}"/>
+    <hyperlink ref="D50" r:id="rId99" xr:uid="{41E06457-0D18-46A5-944D-698E40BE79B1}"/>
+    <hyperlink ref="D51" r:id="rId100" xr:uid="{1F4339E4-23FD-4F71-A2D7-B9A63D2168DC}"/>
+    <hyperlink ref="D52" r:id="rId101" xr:uid="{74C61858-AB0D-40D4-826E-206B16E6BE95}"/>
+    <hyperlink ref="E6" r:id="rId102" xr:uid="{38F1636E-04EF-45FA-A853-30396B0673BC}"/>
+    <hyperlink ref="D6" r:id="rId103" xr:uid="{C2587916-F827-41B7-8EDB-D66AF039E12E}"/>
+    <hyperlink ref="E53" r:id="rId104" xr:uid="{10833195-DF06-4765-8492-81FB0535DD3A}"/>
   </hyperlinks>
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6609,54 +5806,54 @@
   <sheetData>
     <row r="1" spans="1:6" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>456</v>
+        <v>390</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>457</v>
+        <v>391</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>459</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>461</v>
+        <v>395</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>462</v>
+        <v>396</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>463</v>
+        <v>397</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
       <c r="C5" s="21"/>
       <c r="E5" s="21"/>
@@ -6664,50 +5861,50 @@
     </row>
     <row r="6" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>467</v>
+        <v>401</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="C10" s="21"/>
       <c r="E10" s="21"/>
@@ -6715,20 +5912,20 @@
     </row>
     <row r="11" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>470</v>
+        <v>404</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="C12" s="23"/>
       <c r="E12" s="22"/>
@@ -6736,50 +5933,50 @@
     </row>
     <row r="13" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>474</v>
+        <v>408</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>476</v>
+        <v>410</v>
       </c>
       <c r="C17" s="21"/>
       <c r="E17" s="21"/>
@@ -6787,160 +5984,160 @@
     </row>
     <row r="18" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>477</v>
+        <v>411</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>483</v>
+        <v>417</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
     </row>
     <row r="25" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>484</v>
+        <v>418</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>486</v>
+        <v>420</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
     </row>
     <row r="28" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>487</v>
+        <v>421</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
     </row>
     <row r="29" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>488</v>
+        <v>422</v>
       </c>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>490</v>
+        <v>424</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:6" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="C33" s="21"/>
       <c r="E33" s="21"/>
@@ -6948,120 +6145,120 @@
     </row>
     <row r="34" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>494</v>
+        <v>428</v>
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
     </row>
     <row r="36" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
     </row>
     <row r="37" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
     </row>
     <row r="38" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>497</v>
+        <v>431</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
     </row>
     <row r="39" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>498</v>
+        <v>432</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
     </row>
     <row r="40" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>499</v>
+        <v>433</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
     </row>
     <row r="41" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
     </row>
     <row r="42" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
     </row>
     <row r="43" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>500</v>
+        <v>434</v>
       </c>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
     </row>
     <row r="44" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>501</v>
+        <v>435</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:7" s="20" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="20" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>502</v>
+        <v>436</v>
       </c>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
@@ -7519,14 +6716,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D89A625C5B6364BB7302BED22ED65DA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="05bac8ad6e033965382d52c38353e541">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7855343b-5261-4afc-a17c-d4c130fbaa85" xmlns:ns4="72f917e0-5d36-43ac-975d-26afa4cf7fc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="452e5605b09f318b6d66379e79837bd5" ns3:_="" ns4:_="">
     <xsd:import namespace="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
@@ -7773,6 +6962,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
   <ds:schemaRefs>
@@ -7782,16 +6979,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56978299-3DC6-451D-A1E5-57FB07C431CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7808,4 +6995,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Outdoor plants.xlsx
+++ b/data/Outdoor plants.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BE3DB1-27BA-4371-BA64-E2E38D7641AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864A14B6-36A8-4AC0-AEDC-E5B1A128FA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B519764-563C-4CD5-B8E9-9B8B0702B21B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="546">
   <si>
     <t>Plant ID</t>
   </si>
@@ -1385,13 +1385,307 @@
   </si>
   <si>
     <t>https://i.postimg.cc/HxtvL89W/spathodea-campanulata.jpg</t>
+  </si>
+  <si>
+    <t>Cycas revoluta</t>
+  </si>
+  <si>
+    <t>OP-053</t>
+  </si>
+  <si>
+    <t>سيكاس</t>
+  </si>
+  <si>
+    <t>Palms</t>
+  </si>
+  <si>
+    <t>Ficus (Bonsai)</t>
+  </si>
+  <si>
+    <t>فيكس بونساي</t>
+  </si>
+  <si>
+    <t>Ficus lyrata</t>
+  </si>
+  <si>
+    <t>فيكس ليراتا (تينة الكمان)</t>
+  </si>
+  <si>
+    <t>Strelitzia nicolai</t>
+  </si>
+  <si>
+    <t>نجمة الطيور العملاقة</t>
+  </si>
+  <si>
+    <t>فيكس ميكروكاربا</t>
+  </si>
+  <si>
+    <t>زنبق الكانا</t>
+  </si>
+  <si>
+    <t>800 - 1200</t>
+  </si>
+  <si>
+    <t>1100 - 1600</t>
+  </si>
+  <si>
+    <t>Zamia furfuracea</t>
+  </si>
+  <si>
+    <t>زاميا (نخيل الكرتون)</t>
+  </si>
+  <si>
+    <t>Ficus elastica</t>
+  </si>
+  <si>
+    <t>شجرة المطاط</t>
+  </si>
+  <si>
+    <t>OP-054</t>
+  </si>
+  <si>
+    <t>OP-055</t>
+  </si>
+  <si>
+    <t>OP-056</t>
+  </si>
+  <si>
+    <t>OP-057</t>
+  </si>
+  <si>
+    <t>OP-058</t>
+  </si>
+  <si>
+    <t>OP-059</t>
+  </si>
+  <si>
+    <t>OP-060</t>
+  </si>
+  <si>
+    <t>1 - 3 m</t>
+  </si>
+  <si>
+    <t>0.3 - 1 m</t>
+  </si>
+  <si>
+    <t>3 - 12 m</t>
+  </si>
+  <si>
+    <t>6 - 8 m</t>
+  </si>
+  <si>
+    <t>0.6 - 2.4 m</t>
+  </si>
+  <si>
+    <t>3 - 10 m</t>
+  </si>
+  <si>
+    <t>1.5 - 3 m</t>
+  </si>
+  <si>
+    <t>2 - 3.5 m</t>
+  </si>
+  <si>
+    <t>1.5 - 2 m</t>
+  </si>
+  <si>
+    <t>2 - 5 m</t>
+  </si>
+  <si>
+    <t>800-1000 g/year</t>
+  </si>
+  <si>
+    <t>300-500 g/year</t>
+  </si>
+  <si>
+    <t>1500-2000 g/year</t>
+  </si>
+  <si>
+    <t>1800-2500 g/year</t>
+  </si>
+  <si>
+    <t>1800-2200 g/year</t>
+  </si>
+  <si>
+    <t>800-1200 g/year</t>
+  </si>
+  <si>
+    <t>600-900 g/year</t>
+  </si>
+  <si>
+    <t>1600-2100 g/year</t>
+  </si>
+  <si>
+    <t>1100-1300 g/year</t>
+  </si>
+  <si>
+    <t>400-600 g/year</t>
+  </si>
+  <si>
+    <t>2000-3000 g/year</t>
+  </si>
+  <si>
+    <t>2500-3500 g/year</t>
+  </si>
+  <si>
+    <t>2500-3000 g/year</t>
+  </si>
+  <si>
+    <t>1100-1600 g/year</t>
+  </si>
+  <si>
+    <t>800-1100 g/year</t>
+  </si>
+  <si>
+    <t>2200-2800 g/year</t>
+  </si>
+  <si>
+    <t>Ficus microcarpa (panda)</t>
+  </si>
+  <si>
+    <t>Canna generalis</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wT8pc3Nj/Cycas-revoluta.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/5NdVqjz4/Canna-generalis.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/kX3mFDS5/Ficus-(Bonsai).jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/5NdVqjz0/Ficus-elastica.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Nfqc7LXX/Ficus-lyrata.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/pXbHYyjz/Ficus-microcarpa-(panda).jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/28RDF3WQ/Strelitzia-nicolai.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/SNFh7j9d/Zamia-furfuracea.jpg</t>
+  </si>
+  <si>
+    <t>Plectranthus amboinicus</t>
+  </si>
+  <si>
+    <t>الفوطن</t>
+  </si>
+  <si>
+    <t>400 - 650</t>
+  </si>
+  <si>
+    <t>Pelargonium graveolens</t>
+  </si>
+  <si>
+    <t>العطرة</t>
+  </si>
+  <si>
+    <t>550 - 800</t>
+  </si>
+  <si>
+    <t>Rosmarinus officinalis</t>
+  </si>
+  <si>
+    <t>روز ماري</t>
+  </si>
+  <si>
+    <t>500 - 750</t>
+  </si>
+  <si>
+    <t>700 - 1000</t>
+  </si>
+  <si>
+    <t>Cymbopogon citratus</t>
+  </si>
+  <si>
+    <t>عشب الليمون</t>
+  </si>
+  <si>
+    <t>Lavandula angustifolia</t>
+  </si>
+  <si>
+    <t>لافندر</t>
+  </si>
+  <si>
+    <t>550 - 850</t>
+  </si>
+  <si>
+    <t>Salvia officinalis</t>
+  </si>
+  <si>
+    <t>مرامية</t>
+  </si>
+  <si>
+    <t>Myrtus communis</t>
+  </si>
+  <si>
+    <t>حنا الياس</t>
+  </si>
+  <si>
+    <t>OP-061</t>
+  </si>
+  <si>
+    <t>OP-062</t>
+  </si>
+  <si>
+    <t>OP-063</t>
+  </si>
+  <si>
+    <t>OP-064</t>
+  </si>
+  <si>
+    <t>OP-065</t>
+  </si>
+  <si>
+    <t>OP-066</t>
+  </si>
+  <si>
+    <t>OP-067</t>
+  </si>
+  <si>
+    <t>0.5 - 1.5 m</t>
+  </si>
+  <si>
+    <t>500-750 g/year</t>
+  </si>
+  <si>
+    <t>400-650 g/year</t>
+  </si>
+  <si>
+    <t>350-550 g/year</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/L8njHStr/Cymbopogon-citratus.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/kXjx3GSr/Lavandula-angustifolia.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/SNZWFRMB/Myrtus-communis.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Qx6pGCTv/Pelargonium-graveolens.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/X72wSq5n/Plectranthus-amboinicus.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/3JLg5NGY/Rosmarinus-officinalis.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ZKfrtnNb/Salvia-officinalis.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1450,6 +1744,16 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1459,12 +1763,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1473,7 +1792,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1532,8 +1851,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1899,7 +2227,7 @@
     <col min="2" max="2" width="32.453125" style="4" customWidth="1"/>
     <col min="3" max="3" width="23.1796875" style="4" customWidth="1"/>
     <col min="4" max="4" width="12.453125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="47.81640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="54.453125" style="4" customWidth="1"/>
     <col min="6" max="6" width="17.7265625" style="4" customWidth="1"/>
     <col min="7" max="7" width="15.26953125" style="4" customWidth="1"/>
     <col min="8" max="8" width="16.81640625" style="4" bestFit="1" customWidth="1"/>
@@ -5461,91 +5789,1066 @@
       <c r="B53" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="25" t="s">
         <v>442</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="F53" s="28" t="s">
+      <c r="F53" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="G53" s="28" t="s">
+      <c r="G53" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="H53" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I53" s="28" t="s">
+      <c r="H53" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="I53" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="J53" s="28" t="s">
+      <c r="J53" s="25" t="s">
         <v>443</v>
       </c>
-      <c r="K53" s="28" t="s">
+      <c r="K53" s="25" t="s">
         <v>444</v>
       </c>
-      <c r="L53" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="M53" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="N53" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="O53" s="28" t="s">
+      <c r="L53" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M53" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="N53" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O53" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="P53" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q53" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="R53" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="S53" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="T53" s="28" t="s">
+      <c r="P53" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q53" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="R53" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S53" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="T53" s="25" t="s">
         <v>445</v>
       </c>
-      <c r="U53" s="28" t="s">
+      <c r="U53" s="25" t="s">
         <v>446</v>
       </c>
-      <c r="V53" s="28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="55" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14.5" x14ac:dyDescent="0.35"/>
+      <c r="V53" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B54" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>450</v>
+      </c>
+      <c r="D54" s="30"/>
+      <c r="E54" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="F54" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="G54" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J54" s="29" t="s">
+        <v>473</v>
+      </c>
+      <c r="K54" s="29" t="s">
+        <v>473</v>
+      </c>
+      <c r="L54" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M54" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N54" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="P54" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q54" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R54" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S54" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T54" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="U54" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="V54" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B55" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="D55" s="30"/>
+      <c r="E55" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F55" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G55" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J55" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="K55" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="L55" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O55" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P55" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="R55" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S55" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T55" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="U55" s="29" t="s">
+        <v>492</v>
+      </c>
+      <c r="V55" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B56" s="29" t="s">
+        <v>454</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="D56" s="30"/>
+      <c r="E56" s="31" t="s">
+        <v>505</v>
+      </c>
+      <c r="F56" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J56" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="K56" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="L56" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M56" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O56" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P56" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q56" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="R56" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S56" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="T56" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="U56" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="V56" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B57" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="D57" s="30"/>
+      <c r="E57" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J57" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="K57" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="L57" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M57" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N57" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O57" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P57" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q57" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R57" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S57" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="T57" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="U57" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="V57" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B58" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="D58" s="30"/>
+      <c r="E58" s="31" t="s">
+        <v>506</v>
+      </c>
+      <c r="F58" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G58" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J58" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="K58" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L58" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M58" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N58" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O58" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="P58" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q58" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R58" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S58" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="T58" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="U58" s="29" t="s">
+        <v>495</v>
+      </c>
+      <c r="V58" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B59" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="D59" s="30"/>
+      <c r="E59" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="F59" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J59" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="K59" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="L59" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M59" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N59" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O59" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P59" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R59" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S59" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T59" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="U59" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="V59" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B60" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="D60" s="30"/>
+      <c r="E60" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="F60" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H60" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J60" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="K60" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="L60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M60" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O60" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="P60" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q60" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S60" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T60" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="U60" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="V60" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>464</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="D61" s="30"/>
+      <c r="E61" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J61" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="K61" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="L61" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M61" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O61" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="P61" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R61" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S61" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="T61" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="U61" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="V61" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B62" s="29" t="s">
+        <v>509</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="D62" s="30"/>
+      <c r="E62" s="31" t="s">
+        <v>543</v>
+      </c>
+      <c r="F62" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J62" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="K62" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="L62" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M62" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O62" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P62" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q62" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R62" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S62" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T62" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="U62" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="V62" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B63" s="29" t="s">
+        <v>512</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="D63" s="30"/>
+      <c r="E63" s="31" t="s">
+        <v>542</v>
+      </c>
+      <c r="F63" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J63" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="K63" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="L63" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N63" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O63" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P63" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q63" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R63" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S63" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T63" s="29" t="s">
+        <v>492</v>
+      </c>
+      <c r="U63" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="V63" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B64" s="29" t="s">
+        <v>515</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="D64" s="30"/>
+      <c r="E64" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="F64" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I64" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J64" s="29" t="s">
+        <v>535</v>
+      </c>
+      <c r="K64" s="29" t="s">
+        <v>535</v>
+      </c>
+      <c r="L64" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M64" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N64" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O64" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P64" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q64" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R64" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S64" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T64" s="29" t="s">
+        <v>536</v>
+      </c>
+      <c r="U64" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="V64" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="D65" s="30"/>
+      <c r="E65" s="31" t="s">
+        <v>539</v>
+      </c>
+      <c r="F65" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H65" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J65" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="K65" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="L65" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M65" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O65" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P65" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q65" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R65" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S65" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T65" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="U65" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="V65" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B66" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="D66" s="30"/>
+      <c r="E66" s="31" t="s">
+        <v>540</v>
+      </c>
+      <c r="F66" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G66" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J66" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="K66" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="L66" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M66" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N66" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P66" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q66" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R66" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S66" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T66" s="29" t="s">
+        <v>537</v>
+      </c>
+      <c r="U66" s="29" t="s">
+        <v>523</v>
+      </c>
+      <c r="V66" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B67" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>525</v>
+      </c>
+      <c r="D67" s="30"/>
+      <c r="E67" s="31" t="s">
+        <v>545</v>
+      </c>
+      <c r="F67" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I67" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J67" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="K67" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="L67" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M67" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N67" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O67" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P67" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q67" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R67" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S67" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="T67" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="U67" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="V67" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B68" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="D68" s="30"/>
+      <c r="E68" s="31" t="s">
+        <v>541</v>
+      </c>
+      <c r="F68" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I68" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J68" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="K68" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="L68" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M68" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N68" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O68" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P68" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q68" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="R68" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="S68" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="T68" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="U68" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="V68" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="81" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="82" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="83" ht="14.5" x14ac:dyDescent="0.35"/>
@@ -5647,11 +6950,11 @@
     <sortCondition ref="A2:A37"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B51:B52">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B53:B1048576 B46:B50 B37:B38 B20:B35 B1:B14">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51:B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{58D66573-3890-4498-A66F-3227660DC8D7}"/>
@@ -5782,6 +7085,21 @@
     <hyperlink ref="E6" r:id="rId102" xr:uid="{38F1636E-04EF-45FA-A853-30396B0673BC}"/>
     <hyperlink ref="D6" r:id="rId103" xr:uid="{C2587916-F827-41B7-8EDB-D66AF039E12E}"/>
     <hyperlink ref="E53" r:id="rId104" xr:uid="{10833195-DF06-4765-8492-81FB0535DD3A}"/>
+    <hyperlink ref="E54" r:id="rId105" xr:uid="{6B6B6FD5-94FB-4C3F-8C6D-C8F98D39BF55}"/>
+    <hyperlink ref="E59" r:id="rId106" xr:uid="{7A2F8379-D88C-42CF-9E91-A348C4939CD0}"/>
+    <hyperlink ref="E55" r:id="rId107" xr:uid="{17ABCE55-2212-4EAC-9742-C819791C2C70}"/>
+    <hyperlink ref="E61" r:id="rId108" xr:uid="{CF8803C5-144C-4D5F-82DF-F61B938CA47D}"/>
+    <hyperlink ref="E56" r:id="rId109" xr:uid="{1C667421-4AFB-434D-B095-36B1E491B074}"/>
+    <hyperlink ref="E58" r:id="rId110" xr:uid="{0BCCC82D-074A-459C-B18D-9FB4BA4D2B9D}"/>
+    <hyperlink ref="E57" r:id="rId111" xr:uid="{6E2163E2-0911-46D1-9A34-538BC6563894}"/>
+    <hyperlink ref="E60" r:id="rId112" xr:uid="{3E86BEB0-40CE-4260-AC99-EB7BFFB0D05E}"/>
+    <hyperlink ref="E65" r:id="rId113" xr:uid="{F42A429F-D5AD-425E-9219-A70672FE74D5}"/>
+    <hyperlink ref="E66" r:id="rId114" xr:uid="{9DF583C0-6C0B-44DF-8A1F-E70EEC85103F}"/>
+    <hyperlink ref="E68" r:id="rId115" xr:uid="{D7B14A4B-6E71-4186-9719-F317C904BDF8}"/>
+    <hyperlink ref="E63" r:id="rId116" xr:uid="{8756E56E-041E-4F59-9969-C5616368EFD9}"/>
+    <hyperlink ref="E62" r:id="rId117" xr:uid="{B1D664C3-3084-49EE-88BA-925083CE2BB4}"/>
+    <hyperlink ref="E64" r:id="rId118" xr:uid="{26EB60D1-3355-4405-BD5C-5F387663B5A5}"/>
+    <hyperlink ref="E67" r:id="rId119" xr:uid="{8688C54A-1F4E-4850-B6DD-9DA6D3EEA4C5}"/>
   </hyperlinks>
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6707,15 +8025,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D89A625C5B6364BB7302BED22ED65DA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="05bac8ad6e033965382d52c38353e541">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7855343b-5261-4afc-a17c-d4c130fbaa85" xmlns:ns4="72f917e0-5d36-43ac-975d-26afa4cf7fc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="452e5605b09f318b6d66379e79837bd5" ns3:_="" ns4:_="">
     <xsd:import namespace="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
@@ -6962,6 +8271,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6971,14 +8289,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56978299-3DC6-451D-A1E5-57FB07C431CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6997,6 +8307,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
   <ds:schemaRefs>

--- a/data/Outdoor plants.xlsx
+++ b/data/Outdoor plants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864A14B6-36A8-4AC0-AEDC-E5B1A128FA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566B3271-D440-4C8C-882E-FCF0EA4D4E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B519764-563C-4CD5-B8E9-9B8B0702B21B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="569">
   <si>
     <t>Plant ID</t>
   </si>
@@ -1423,12 +1423,6 @@
     <t>زنبق الكانا</t>
   </si>
   <si>
-    <t>800 - 1200</t>
-  </si>
-  <si>
-    <t>1100 - 1600</t>
-  </si>
-  <si>
     <t>Zamia furfuracea</t>
   </si>
   <si>
@@ -1576,30 +1570,18 @@
     <t>الفوطن</t>
   </si>
   <si>
-    <t>400 - 650</t>
-  </si>
-  <si>
     <t>Pelargonium graveolens</t>
   </si>
   <si>
     <t>العطرة</t>
   </si>
   <si>
-    <t>550 - 800</t>
-  </si>
-  <si>
     <t>Rosmarinus officinalis</t>
   </si>
   <si>
     <t>روز ماري</t>
   </si>
   <si>
-    <t>500 - 750</t>
-  </si>
-  <si>
-    <t>700 - 1000</t>
-  </si>
-  <si>
     <t>Cymbopogon citratus</t>
   </si>
   <si>
@@ -1612,9 +1594,6 @@
     <t>لافندر</t>
   </si>
   <si>
-    <t>550 - 850</t>
-  </si>
-  <si>
     <t>Salvia officinalis</t>
   </si>
   <si>
@@ -1679,6 +1658,96 @@
   </si>
   <si>
     <t>https://i.postimg.cc/ZKfrtnNb/Salvia-officinalis.jpg</t>
+  </si>
+  <si>
+    <t>Pleioblastus spp.</t>
+  </si>
+  <si>
+    <t>بامبو (بليوبلاستوس)</t>
+  </si>
+  <si>
+    <t>Schefflera arboricola</t>
+  </si>
+  <si>
+    <t>شيفليرا</t>
+  </si>
+  <si>
+    <t>Bismarckia nobilis</t>
+  </si>
+  <si>
+    <t>نخيل بسمارك</t>
+  </si>
+  <si>
+    <t>Dypsis lutescens</t>
+  </si>
+  <si>
+    <t>نخيل أريكا</t>
+  </si>
+  <si>
+    <t>550-800 g/year</t>
+  </si>
+  <si>
+    <t>700-1000 g/year</t>
+  </si>
+  <si>
+    <t>550-850 g/year</t>
+  </si>
+  <si>
+    <t>2800-5000 g/year</t>
+  </si>
+  <si>
+    <t>4000-7000 g/year</t>
+  </si>
+  <si>
+    <t>2800-4200 g/year</t>
+  </si>
+  <si>
+    <t>2000-3500 g/year</t>
+  </si>
+  <si>
+    <t>3000-5000 g/year</t>
+  </si>
+  <si>
+    <t>1 - 5 m</t>
+  </si>
+  <si>
+    <t>4 - 5 m</t>
+  </si>
+  <si>
+    <t>2.5 - 4 m</t>
+  </si>
+  <si>
+    <t>3 - 4 m</t>
+  </si>
+  <si>
+    <t>10 - 18 m</t>
+  </si>
+  <si>
+    <t>6 - 9 m</t>
+  </si>
+  <si>
+    <t>OP-068</t>
+  </si>
+  <si>
+    <t>OP-069</t>
+  </si>
+  <si>
+    <t>OP-070</t>
+  </si>
+  <si>
+    <t>OP-071</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wvzDhbPP/Bismarckia-nobilis.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/d1FG8SXg/Dypsis-lutescens.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/RFmwcby5/Pleioblastus-spp.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/cHWfQ5jV/Schefflera-arboricola.jpg</t>
   </si>
 </sst>
 </file>
@@ -1792,7 +1861,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1851,16 +1920,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5859,7 +5931,7 @@
       </c>
       <c r="D54" s="30"/>
       <c r="E54" s="31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F54" s="29" t="s">
         <v>451</v>
@@ -5874,10 +5946,10 @@
         <v>126</v>
       </c>
       <c r="J54" s="29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K54" s="29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L54" s="29" t="s">
         <v>31</v>
@@ -5904,10 +5976,10 @@
         <v>28</v>
       </c>
       <c r="T54" s="29" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="U54" s="29" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="V54" s="25" t="s">
         <v>31</v>
@@ -5915,7 +5987,7 @@
     </row>
     <row r="55" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B55" s="29" t="s">
         <v>452</v>
@@ -5925,7 +5997,7 @@
       </c>
       <c r="D55" s="30"/>
       <c r="E55" s="31" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F55" s="29" t="s">
         <v>70</v>
@@ -5940,10 +6012,10 @@
         <v>126</v>
       </c>
       <c r="J55" s="29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K55" s="29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L55" s="29" t="s">
         <v>31</v>
@@ -5970,10 +6042,10 @@
         <v>28</v>
       </c>
       <c r="T55" s="29" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="U55" s="29" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="V55" s="25" t="s">
         <v>31</v>
@@ -5981,7 +6053,7 @@
     </row>
     <row r="56" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B56" s="29" t="s">
         <v>454</v>
@@ -5991,7 +6063,7 @@
       </c>
       <c r="D56" s="30"/>
       <c r="E56" s="31" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F56" s="29" t="s">
         <v>133</v>
@@ -6006,10 +6078,10 @@
         <v>29</v>
       </c>
       <c r="J56" s="29" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K56" s="29" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L56" s="29" t="s">
         <v>31</v>
@@ -6036,10 +6108,10 @@
         <v>45</v>
       </c>
       <c r="T56" s="29" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="U56" s="29" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="V56" s="25" t="s">
         <v>31</v>
@@ -6047,7 +6119,7 @@
     </row>
     <row r="57" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B57" s="29" t="s">
         <v>456</v>
@@ -6057,7 +6129,7 @@
       </c>
       <c r="D57" s="30"/>
       <c r="E57" s="31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>70</v>
@@ -6072,10 +6144,10 @@
         <v>53</v>
       </c>
       <c r="J57" s="29" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K57" s="29" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L57" s="29" t="s">
         <v>31</v>
@@ -6102,10 +6174,10 @@
         <v>45</v>
       </c>
       <c r="T57" s="29" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="U57" s="29" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="V57" s="25" t="s">
         <v>31</v>
@@ -6113,17 +6185,17 @@
     </row>
     <row r="58" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C58" s="28" t="s">
         <v>458</v>
       </c>
       <c r="D58" s="30"/>
       <c r="E58" s="31" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F58" s="29" t="s">
         <v>133</v>
@@ -6168,10 +6240,10 @@
         <v>45</v>
       </c>
       <c r="T58" s="29" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="U58" s="29" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="V58" s="25" t="s">
         <v>31</v>
@@ -6179,17 +6251,17 @@
     </row>
     <row r="59" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B59" s="29" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C59" s="28" t="s">
         <v>459</v>
       </c>
       <c r="D59" s="30"/>
       <c r="E59" s="31" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>26</v>
@@ -6204,10 +6276,10 @@
         <v>53</v>
       </c>
       <c r="J59" s="29" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K59" s="29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L59" s="29" t="s">
         <v>31</v>
@@ -6234,10 +6306,10 @@
         <v>28</v>
       </c>
       <c r="T59" s="29" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="U59" s="29" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="V59" s="25" t="s">
         <v>31</v>
@@ -6245,17 +6317,17 @@
     </row>
     <row r="60" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B60" s="29" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D60" s="30"/>
       <c r="E60" s="31" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>451</v>
@@ -6273,7 +6345,7 @@
         <v>54</v>
       </c>
       <c r="K60" s="29" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L60" s="29" t="s">
         <v>31</v>
@@ -6300,10 +6372,10 @@
         <v>28</v>
       </c>
       <c r="T60" s="29" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="U60" s="29" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="V60" s="25" t="s">
         <v>31</v>
@@ -6311,17 +6383,17 @@
     </row>
     <row r="61" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B61" s="29" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="31" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F61" s="29" t="s">
         <v>133</v>
@@ -6336,10 +6408,10 @@
         <v>29</v>
       </c>
       <c r="J61" s="29" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K61" s="29" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L61" s="29" t="s">
         <v>31</v>
@@ -6366,10 +6438,10 @@
         <v>45</v>
       </c>
       <c r="T61" s="29" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="U61" s="29" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="V61" s="25" t="s">
         <v>31</v>
@@ -6377,17 +6449,17 @@
     </row>
     <row r="62" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B62" s="29" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D62" s="30"/>
       <c r="E62" s="31" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F62" s="29" t="s">
         <v>26</v>
@@ -6432,10 +6504,10 @@
         <v>28</v>
       </c>
       <c r="T62" s="29" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="U62" s="29" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="V62" s="25" t="s">
         <v>31</v>
@@ -6443,17 +6515,17 @@
     </row>
     <row r="63" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D63" s="30"/>
       <c r="E63" s="31" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F63" s="29" t="s">
         <v>70</v>
@@ -6498,10 +6570,10 @@
         <v>28</v>
       </c>
       <c r="T63" s="29" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="U63" s="29" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="V63" s="25" t="s">
         <v>31</v>
@@ -6509,17 +6581,17 @@
     </row>
     <row r="64" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D64" s="30"/>
       <c r="E64" s="31" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F64" s="29" t="s">
         <v>70</v>
@@ -6534,10 +6606,10 @@
         <v>53</v>
       </c>
       <c r="J64" s="29" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="K64" s="29" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="L64" s="29" t="s">
         <v>31</v>
@@ -6564,10 +6636,10 @@
         <v>28</v>
       </c>
       <c r="T64" s="29" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="U64" s="29" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="V64" s="25" t="s">
         <v>31</v>
@@ -6575,17 +6647,17 @@
     </row>
     <row r="65" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D65" s="30"/>
       <c r="E65" s="31" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="F65" s="29" t="s">
         <v>80</v>
@@ -6630,10 +6702,10 @@
         <v>28</v>
       </c>
       <c r="T65" s="29" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="U65" s="29" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="V65" s="25" t="s">
         <v>31</v>
@@ -6641,17 +6713,17 @@
     </row>
     <row r="66" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D66" s="30"/>
       <c r="E66" s="31" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="F66" s="29" t="s">
         <v>70</v>
@@ -6696,10 +6768,10 @@
         <v>28</v>
       </c>
       <c r="T66" s="29" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="U66" s="29" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="V66" s="25" t="s">
         <v>31</v>
@@ -6707,17 +6779,17 @@
     </row>
     <row r="67" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="D67" s="30"/>
       <c r="E67" s="31" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="F67" s="29" t="s">
         <v>70</v>
@@ -6762,10 +6834,10 @@
         <v>28</v>
       </c>
       <c r="T67" s="29" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="U67" s="29" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="V67" s="25" t="s">
         <v>31</v>
@@ -6773,17 +6845,17 @@
     </row>
     <row r="68" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="D68" s="30"/>
       <c r="E68" s="31" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F68" s="29" t="s">
         <v>70</v>
@@ -6798,10 +6870,10 @@
         <v>53</v>
       </c>
       <c r="J68" s="29" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K68" s="29" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L68" s="29" t="s">
         <v>31</v>
@@ -6828,19 +6900,275 @@
         <v>45</v>
       </c>
       <c r="T68" s="29" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="U68" s="29" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="V68" s="25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J69" s="32" t="s">
+        <v>555</v>
+      </c>
+      <c r="K69" s="32" t="s">
+        <v>471</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q69" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S69" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T69" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="U69" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="V69" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="32" t="s">
+        <v>558</v>
+      </c>
+      <c r="K70" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q70" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R70" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S70" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T70" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="U70" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="V70" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J71" s="32" t="s">
+        <v>559</v>
+      </c>
+      <c r="K71" s="32" t="s">
+        <v>556</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q71" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S71" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T71" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="U71" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="V71" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J72" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="K72" s="32" t="s">
+        <v>557</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q72" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S72" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T72" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="U72" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="V72" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="73" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="74" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="75" spans="1:22" ht="14.5" x14ac:dyDescent="0.35"/>
@@ -7100,6 +7428,10 @@
     <hyperlink ref="E62" r:id="rId117" xr:uid="{B1D664C3-3084-49EE-88BA-925083CE2BB4}"/>
     <hyperlink ref="E64" r:id="rId118" xr:uid="{26EB60D1-3355-4405-BD5C-5F387663B5A5}"/>
     <hyperlink ref="E67" r:id="rId119" xr:uid="{8688C54A-1F4E-4850-B6DD-9DA6D3EEA4C5}"/>
+    <hyperlink ref="E71" r:id="rId120" xr:uid="{51A47B13-011E-43FD-975A-5C3D8237F4A3}"/>
+    <hyperlink ref="E72" r:id="rId121" xr:uid="{763D40BA-75BC-43FC-87EB-D7D75D422829}"/>
+    <hyperlink ref="E69" r:id="rId122" xr:uid="{C27BBE41-59F1-4E3F-96DE-1740CCB8DB94}"/>
+    <hyperlink ref="E70" r:id="rId123" xr:uid="{58196322-500B-47C9-A791-6A656264F129}"/>
   </hyperlinks>
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8025,6 +8357,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D89A625C5B6364BB7302BED22ED65DA" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="05bac8ad6e033965382d52c38353e541">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7855343b-5261-4afc-a17c-d4c130fbaa85" xmlns:ns4="72f917e0-5d36-43ac-975d-26afa4cf7fc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="452e5605b09f318b6d66379e79837bd5" ns3:_="" ns4:_="">
     <xsd:import namespace="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
@@ -8271,24 +8620,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7855343b-5261-4afc-a17c-d4c130fbaa85" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56978299-3DC6-451D-A1E5-57FB07C431CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8305,22 +8655,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE4A15A-EC2D-4537-B6DC-2F235DBE6314}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53F9CFB-0E7D-4BF1-9CBE-0D133C6536E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7855343b-5261-4afc-a17c-d4c130fbaa85"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>